--- a/data/output/eventos_processados.xlsx
+++ b/data/output/eventos_processados.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW124"/>
+  <dimension ref="A1:AX124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,15 +662,20 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
+          <t>publicar_webgis</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
           <t>fonte_web</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>confianca_web</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>justificativa_web</t>
         </is>
@@ -853,9 +858,12 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+      <c r="AU2" t="b">
+        <v>1</v>
+      </c>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1038,15 +1046,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AU3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>https://www.floripashopping.com.br/localizacao.php?lang=sp</t>
         </is>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>0.97</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>A fonte oficial do shopping informa a localização do Floripa Shopping em Florianópolis (SC), e uma cobertura do evento identifica o Festival de Circo de Florianópolis acontecendo na Praça de Eventos do Floripa Shopping, no endereço Rodovia SC-401, 3.116, Saco Grande, Florianópolis. Como o usuário informou apenas 'Floripa Shopping', o espaço provável é o próprio shopping; o endereço e bairro foram confirmados por fonte web confiável.</t>
         </is>
@@ -1227,15 +1238,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
+      <c r="AU4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>https://www.cultura.sc.gov.br/noticias/18496-18496-horario-de-funcionamento-dos-espacos-culturais-administrados-pela-fcc</t>
         </is>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>0.97</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Há evidência consistente de que o 'Cinema do CIC' corresponde ao Cinema/Sala Gilberto Gerlach no Centro Integrado de Cultura (CIC), em Florianópolis. A fonte oficial da FCC informa o CIC na Av. Gov. Irineu Bornhausen, 5600, bairro Agronômica, Florianópolis/SC.</t>
         </is>
@@ -1414,15 +1428,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
+      <c r="AU5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>https://cultura.sc.gov.br/noticias/18496-18496-horario-de-funcionamento-dos-espacos-culturais-administrados-pela-fcc</t>
         </is>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>0.95</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>O local informado “Teatro do CIC” corresponde ao complexo Centro Integrado de Cultura (CIC), onde fica o Teatro Ademir Rosa. A fonte consultada informa o endereço no CIC, em Florianópolis, na Avenida Governador Irineu Bornhausen, 5600, bairro Agronômica.</t>
         </is>
@@ -1601,9 +1618,12 @@
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
+      <c r="AU6" t="b">
+        <v>1</v>
+      </c>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1778,9 +1798,12 @@
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
+      <c r="AU7" t="b">
+        <v>1</v>
+      </c>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1955,9 +1978,12 @@
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
+      <c r="AU8" t="b">
+        <v>1</v>
+      </c>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2136,9 +2162,12 @@
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
+      <c r="AU9" t="b">
+        <v>1</v>
+      </c>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2323,15 +2352,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
+      <c r="AU10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/agenda/restaurantes</t>
         </is>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>A fonte consultada associa o evento "Marisco Social" ao "Centro de Eventos Oceania" e informa o endereço "R. do Marisco, 550 - Ingleses, Florianópolis"; outras fontes também reforçam "Rua do Marisco, 550, bairro Ingleses, Florianópolis/SC".</t>
         </is>
@@ -2518,15 +2550,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU11" t="inlineStr">
+      <c r="AU11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>https://www.floripashopping.com.br/localizacao.php?lang=pt</t>
         </is>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>0.96</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>O site oficial do Floripa Shopping informa dois acessos/endereço no bairro Saco Grande, em Florianópolis. Como o evento foi informado apenas como ocorrendo no Floripa Shopping, esse é o local mais provável com base na fonte oficial.</t>
         </is>
@@ -2705,15 +2740,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU12" t="inlineStr">
+      <c r="AU12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>https://www.sc.gov.br/servicos/reservar-pauta-no-teatro-ademir-rosa-cic-no-teatro-alvaro-de-carvalho-tac-e-no-teatro-pedro-ivo</t>
         </is>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>0.93</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>O 'Teatro do CIC' corresponde ao Teatro Ademir Rosa, que fica no Centro Integrado de Cultura (CIC). A fonte oficial do governo de SC informa o endereço e o bairro como Saco Grande para o serviço de reserva da pauta do teatro; porém outras fontes oficiais do próprio estado e da FCC situam o CIC em Avenida Governador Irineu Bornhausen, 5600, Agronômica. Como o pedido é para o local do evento e o nome informado foi genérico ('Teatro do CIC'), a identificação mais provável é o Teatro Ademir Rosa no CIC, com endereço Av. Gov. Irineu Bornhausen, 5600, Agronômica, Florianópolis.</t>
         </is>
@@ -2896,9 +2934,12 @@
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
+      <c r="AU13" t="b">
+        <v>1</v>
+      </c>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3073,9 +3114,12 @@
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
+      <c r="AU14" t="b">
+        <v>1</v>
+      </c>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3256,15 +3300,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU15" t="inlineStr">
+      <c r="AU15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="inlineStr">
         <is>
           <t>https://www.sesc-sc.com.br/sescsc/conteudo/documentos/guia-de-servicos-1-semestre-2026-sesc-prainha.pdf</t>
         </is>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>A fonte oficial do Sesc-SC identifica o Sesc Prainha em Florianópolis com endereço na Travessa Siryaco Atherino, 100 - Centro, e a agenda do evento informa que as atividades do 'Sesc Celebra 80 anos' ocorrem no 'Ginásio Sesc Prainha'. Como o pedido é para localizar o espaço do evento, o nome provável é Sesc Prainha e o bairro é Centro. Se desejar, posso também buscar a referência local mais próxima dentro do entorno imediato, mas sem inventar dados.</t>
         </is>
@@ -3451,9 +3498,12 @@
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
+      <c r="AU16" t="b">
+        <v>1</v>
+      </c>
       <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3632,9 +3682,12 @@
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
+      <c r="AU17" t="b">
+        <v>1</v>
+      </c>
       <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3817,15 +3870,18 @@
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr">
+      <c r="AU18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV18" t="inlineStr">
         <is>
           <t>https://cervejariabugio.com.br/?store_id=2</t>
         </is>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>0.96</v>
       </c>
-      <c r="AW18" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>O evento "Vozes à Solta — oficina de canto" aparece na programação do perfil @bugiocentro, e a página oficial da Cervejaria Bugio informa que o Centro Bugio fica na Rua Victor Meirelles, 112, Centro Histórico/Centro, Florianópolis. A informação é corroborada por páginas de eventos que apontam o mesmo local e endereço.</t>
         </is>
@@ -4012,9 +4068,12 @@
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
+      <c r="AU19" t="b">
+        <v>1</v>
+      </c>
       <c r="AV19" t="inlineStr"/>
       <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4197,9 +4256,12 @@
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
+      <c r="AU20" t="b">
+        <v>1</v>
+      </c>
       <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4382,9 +4444,12 @@
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
+      <c r="AU21" t="b">
+        <v>1</v>
+      </c>
       <c r="AV21" t="inlineStr"/>
       <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4563,9 +4628,12 @@
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
+      <c r="AU22" t="b">
+        <v>1</v>
+      </c>
       <c r="AV22" t="inlineStr"/>
       <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4748,9 +4816,12 @@
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
+      <c r="AU23" t="b">
+        <v>1</v>
+      </c>
       <c r="AV23" t="inlineStr"/>
       <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4929,15 +5000,18 @@
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr">
+      <c r="AU24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/72270-quarteto-marimbondo-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AV24" t="n">
+      <c r="AW24" t="n">
         <v>0.96</v>
       </c>
-      <c r="AW24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Há evidência direta de que o evento “Vinilaria Bugio” ocorre no Bugio Centro, com endereço R. Victor Meirelles, 112, no bairro Centro, Florianópolis. A fonte também relaciona o perfil @bugiocentro ao local do evento. Como há correspondência explícita entre o evento e o espaço, a confiança é alta.</t>
         </is>
@@ -5114,15 +5188,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU25" t="inlineStr">
+      <c r="AU25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="inlineStr">
         <is>
           <t>https://www.cervejariabugio.com.br/</t>
         </is>
       </c>
-      <c r="AV25" t="n">
+      <c r="AW25" t="n">
         <v>0.76</v>
       </c>
-      <c r="AW25" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>O perfil @bugiolab e as buscas retornaram evidências para "Bugio"/"Bugio Lab" em Florianópolis; o site oficial da Cervejaria Bugio informa que o Centro Bugio fica no centro histórico de Florianópolis, na esquina da rua Victor Meirelles com a Nunes Machado. Não encontrei uma página oficial separada que confirme o nome exatamente como "bugiolab", então a identificação é provável, não absoluta.</t>
         </is>
@@ -5297,9 +5374,12 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU26" t="inlineStr"/>
+      <c r="AU26" t="b">
+        <v>1</v>
+      </c>
       <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Não encontrei evidência confiável que vincule “bugiolab” a um estabelecimento específico em Florianópolis. As buscas retornaram resultados não relacionados ou insuficientes para confirmar nome, endereço e bairro sem inventar informações.</t>
         </is>
@@ -5474,9 +5554,12 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU27" t="inlineStr"/>
+      <c r="AU27" t="b">
+        <v>1</v>
+      </c>
       <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Não encontrei evidência confiável que conecte explicitamente o perfil @bugiolab ao local do evento em Florianópolis. As buscas retornaram resultados genéricos de Google Maps sem confirmação do estabelecimento/espaco correspondente a 'bugiolab'. Para não inventar endereço ou bairro, retorno null.</t>
         </is>
@@ -5659,15 +5742,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU28" t="inlineStr">
+      <c r="AU28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="inlineStr">
         <is>
           <t>https://www.cervejariabugio.com.br/</t>
         </is>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>0.96</v>
       </c>
-      <c r="AW28" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>O site oficial informa que o “Centro Bugio” fica no centro histórico de Florianópolis e traz o endereço “Rua Victor Meirelles, 112, Centro Histórico”. Isso corresponde ao local provável do evento associado ao perfil @bugiolab.</t>
         </is>
@@ -5776,9 +5862,12 @@
           <t>Local não encontrado na HERE nem na pesquisa web</t>
         </is>
       </c>
-      <c r="AU29" t="inlineStr"/>
+      <c r="AU29" t="b">
+        <v>1</v>
+      </c>
       <c r="AV29" t="inlineStr"/>
       <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5883,9 +5972,12 @@
           <t>Local não encontrado na HERE nem na pesquisa web</t>
         </is>
       </c>
-      <c r="AU30" t="inlineStr"/>
+      <c r="AU30" t="b">
+        <v>1</v>
+      </c>
       <c r="AV30" t="inlineStr"/>
       <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6068,9 +6160,12 @@
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
+      <c r="AU31" t="b">
+        <v>1</v>
+      </c>
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6245,15 +6340,18 @@
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr">
+      <c r="AU32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/76708-forro-da-nati-bugio-trindade-florianopolis</t>
         </is>
       </c>
-      <c r="AV32" t="n">
+      <c r="AW32" t="n">
         <v>0.95</v>
       </c>
-      <c r="AW32" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>O evento "Forró da Nati + chope em dobro" aparece associado ao perfil @bugiotrindade e à casa "Bugio Trindade". A fonte consultada informa explicitamente o endereço completo e o bairro Trindade, em Florianópolis.</t>
         </is>
@@ -6440,9 +6538,12 @@
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
+      <c r="AU33" t="b">
+        <v>1</v>
+      </c>
       <c r="AV33" t="inlineStr"/>
       <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6625,15 +6726,18 @@
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr">
+      <c r="AU34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV34" t="inlineStr">
         <is>
           <t>https://www.vaidancar.com.br/baile/details/BLDVzNETPy</t>
         </is>
       </c>
-      <c r="AV34" t="n">
+      <c r="AW34" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW34" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>O evento "Trio Sambachoro" aparece associado ao Bugio Centro, com a localização explicitada em Rua Victor Meirelles, 112, Centro, Florianópolis - SC. A menção ao "Largo da Antonieta" nos eventos do mesmo perfil reforça que o espaço fica nessa área do Centro de Florianópolis.</t>
         </is>
@@ -6818,15 +6922,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU35" t="inlineStr">
+      <c r="AU35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="inlineStr">
         <is>
           <t>https://www.cervejariabugio.com.br/ ; https://troop.is/events/naddr1qvzqqqrukvpzp08t5xjg49jvqg77q54d5smmjastaq8d85zzuwtzdzr0m6fd0z0xqqsxxcecxgun2dp5vscnsvejxqerzwfhxvekydpsv5ursvtyxe3kvcggq9v23 ; https://www.tripadvisor.com.br/Restaurant_Review-g303576-d33047585-Reviews-Bugio_Centro-Florianopolis_State_of_Santa_Catarina.html</t>
         </is>
       </c>
-      <c r="AV35" t="n">
+      <c r="AW35" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW35" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Encontrei evidência de que o Bugio Lab fica no Bugio Centro, em Florianópolis, no endereço Rua Victor Meirelles, 112, segundo piso; outras fontes reforçam o mesmo endereço para Bugio Centro e situam o estabelecimento no bairro Centro. A identificação do nome 'Bugio Lab' como espaço ligado ao Bugio Centro é consistente com as fontes encontradas. Nenhuma fonte confiável indicou outro endereço.</t>
         </is>
@@ -7013,9 +7120,12 @@
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
+      <c r="AU36" t="b">
+        <v>1</v>
+      </c>
       <c r="AV36" t="inlineStr"/>
       <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7194,9 +7304,12 @@
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr"/>
+      <c r="AU37" t="b">
+        <v>1</v>
+      </c>
       <c r="AV37" t="inlineStr"/>
       <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7393,15 +7506,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU38" t="inlineStr">
+      <c r="AU38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV38" t="inlineStr">
         <is>
           <t>https://www.baiacudealguem.com.br/category/associacao-cultural/</t>
         </is>
       </c>
-      <c r="AV38" t="n">
+      <c r="AW38" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW38" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>A página oficial da Associação Cultural Baiacu de Alguém informa o endereço completo da sede como Rua Padre Lourenço R. de Andrade, 650 – Santo Antônio de Lisboa – Florianópolis (SC), confirmando o local informado do evento.</t>
         </is>
@@ -7592,9 +7708,12 @@
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
+      <c r="AU39" t="b">
+        <v>1</v>
+      </c>
       <c r="AV39" t="inlineStr"/>
       <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7785,9 +7904,12 @@
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
-      <c r="AU40" t="inlineStr"/>
+      <c r="AU40" t="b">
+        <v>1</v>
+      </c>
       <c r="AV40" t="inlineStr"/>
       <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7974,9 +8096,12 @@
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="inlineStr"/>
+      <c r="AU41" t="b">
+        <v>1</v>
+      </c>
       <c r="AV41" t="inlineStr"/>
       <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8163,9 +8288,12 @@
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
-      <c r="AU42" t="inlineStr"/>
+      <c r="AU42" t="b">
+        <v>1</v>
+      </c>
       <c r="AV42" t="inlineStr"/>
       <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8340,15 +8468,18 @@
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
-      <c r="AU43" t="inlineStr">
+      <c r="AU43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV43" t="inlineStr">
         <is>
           <t>https://fundacaoculturalbadesc.com/</t>
         </is>
       </c>
-      <c r="AV43" t="n">
+      <c r="AW43" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW43" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>A página oficial da Fundação Cultural Badesc informa que a instituição fica na Rua Visconde de Ouro Preto, 216, Centro, Florianópolis/SC, e o conteúdo sobre a exposição 'Ressonâncias do Gesto' indica que ela ocupa o Espaço 3 da própria Fundação. A evidência é consistente e direta, por isso o espaço provável é a Fundação Cultural Badesc, no bairro Centro.</t>
         </is>
@@ -8541,15 +8672,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU44" t="inlineStr">
+      <c r="AU44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV44" t="inlineStr">
         <is>
           <t>https://www.cylex.com.br/florianopolis/associa%C3%A7%C3%A3o-cultural-baiacu-de-alguem-11871181.html</t>
         </is>
       </c>
-      <c r="AV44" t="n">
+      <c r="AW44" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW44" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Encontrei uma listagem do estabelecimento em Florianópolis com o nome Associação Cultural Baiacu de Alguem/Baiacu de Alguém, no endereço Rua Pe Lourenço R. de Andrade 650, 88050-400, em Santo Antônio de Lisboa. A informação é consistente com outras referências encontradas para o Baiacu de Alguém em Santo Antônio de Lisboa, mas a fonte direta do endereço é a listagem consultada.</t>
         </is>
@@ -8734,15 +8868,18 @@
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr">
+      <c r="AU45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV45" t="inlineStr">
         <is>
           <t>https://www.baiacudealguem.com.br/pescadores-de-cultura/</t>
         </is>
       </c>
-      <c r="AV45" t="n">
+      <c r="AW45" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW45" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>A fonte oficial do coletivo/associação Baiacu de Alguém informa explicitamente o endereço Rua Padre Lourenço R. de Andrade, 650 – Santo Antônio de Lisboa – Florianópolis (SC). Outras fontes consultadas reforçam o mesmo local como 'Espaço Cultural Baiacu de Alguém' no bairro Santo Antônio de Lisboa. Como você pediu para não inventar endereço, usei apenas o que aparece com evidência convergente na web.</t>
         </is>
@@ -8921,9 +9058,12 @@
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
-      <c r="AU46" t="inlineStr"/>
+      <c r="AU46" t="b">
+        <v>1</v>
+      </c>
       <c r="AV46" t="inlineStr"/>
       <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9098,9 +9238,12 @@
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="inlineStr"/>
+      <c r="AU47" t="b">
+        <v>1</v>
+      </c>
       <c r="AV47" t="inlineStr"/>
       <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9281,15 +9424,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU48" t="inlineStr">
+      <c r="AU48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV48" t="inlineStr">
         <is>
           <t>https://www.vaidancar.com.br/baile/details/BLDVzNETPy</t>
         </is>
       </c>
-      <c r="AV48" t="n">
+      <c r="AW48" t="n">
         <v>0.91</v>
       </c>
-      <c r="AW48" t="inlineStr">
+      <c r="AX48" t="inlineStr">
         <is>
           <t xml:space="preserve">O evento 'Trio Sambachoro' aparece associado ao Bugio Centro, com localização explicitada como Rua Victor Meirelles, 112, Centro - Florianópolis - SC. Outras fontes sobre o Largo da Antonieta situam o espaço no Centro-Leste de Florianópolis, entre as ruas Vítor Meirelles e Nunes Machado, reforçando a identificação do local. </t>
         </is>
@@ -9476,9 +9622,12 @@
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
-      <c r="AU49" t="inlineStr"/>
+      <c r="AU49" t="b">
+        <v>1</v>
+      </c>
       <c r="AV49" t="inlineStr"/>
       <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9657,9 +9806,12 @@
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr"/>
+      <c r="AU50" t="b">
+        <v>1</v>
+      </c>
       <c r="AV50" t="inlineStr"/>
       <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9838,15 +9990,18 @@
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr">
+      <c r="AU51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV51" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/72270-quarteto-marimbondo-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AV51" t="n">
+      <c r="AW51" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW51" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>A evidência mais direta indica que o evento Vinilaria Bugio ocorre no Largo da Antonieta em frente ao Bugio Centro, e a página do evento lista o endereço do Bugio Centro como Rua Victor Meirelles, 112, Centro, Florianópolis. Há também fontes complementares confirmando o Largo da Antonieta como área em frente ao Bar Bugio.</t>
         </is>
@@ -10035,15 +10190,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU52" t="inlineStr">
+      <c r="AU52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV52" t="inlineStr">
         <is>
           <t>https://dceven.ufsc.br/localizacao/</t>
         </is>
       </c>
-      <c r="AV52" t="n">
+      <c r="AW52" t="n">
         <v>0.87</v>
       </c>
-      <c r="AW52" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>A fonte oficial da UFSC indica a localização do campus Florianópolis como Trindade. Como o evento foi descrito apenas como ocorrendo nos arredores da UFSC, a identificação mais provável é o campus principal da UFSC em Trindade. Não encontrei evidência confiável para um endereço mais específico dentro dos arredores do campus.</t>
         </is>
@@ -10218,9 +10376,12 @@
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
+      <c r="AU53" t="b">
+        <v>1</v>
+      </c>
       <c r="AV53" t="inlineStr"/>
       <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10395,9 +10556,12 @@
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
-      <c r="AU54" t="inlineStr"/>
+      <c r="AU54" t="b">
+        <v>1</v>
+      </c>
       <c r="AV54" t="inlineStr"/>
       <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10576,15 +10740,18 @@
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
-      <c r="AU55" t="inlineStr">
+      <c r="AU55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV55" t="inlineStr">
         <is>
           <t>https://troop.is/events/naddr1qvzqqqrukvpzp08t5xjg49jvqg77q54d5smmjastaq8d85zzuwtzdzr0m6fd0z0xqqsrsdn9xv6xxvpcxv6rwcm9vvmxzwf4xanxzc3hxpjkywrpxcurqeshrhdsl</t>
         </is>
       </c>
-      <c r="AV55" t="n">
+      <c r="AW55" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW55" t="inlineStr">
+      <c r="AX55" t="inlineStr">
         <is>
           <t>A fonte consultada associa o evento 'Vinilaria Bugio' ao 'Largo da Antonieta' dentro da Bugio Centro e informa a localização da casa como 'Bugio Centro, R. Victor Meirelles, 112'. Outras fontes reforçam que o Largo da Antonieta fica na Rua Victor Meirelles, no Centro de Florianópolis. Como há evidência convergente, o endereço e bairro mais prováveis são estes.</t>
         </is>
@@ -10767,9 +10934,12 @@
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
-      <c r="AU56" t="inlineStr"/>
+      <c r="AU56" t="b">
+        <v>1</v>
+      </c>
       <c r="AV56" t="inlineStr"/>
       <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10948,9 +11118,12 @@
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
-      <c r="AU57" t="inlineStr"/>
+      <c r="AU57" t="b">
+        <v>1</v>
+      </c>
       <c r="AV57" t="inlineStr"/>
       <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11059,9 +11232,12 @@
           <t>Local não encontrado na HERE nem na pesquisa web</t>
         </is>
       </c>
-      <c r="AU58" t="inlineStr"/>
+      <c r="AU58" t="b">
+        <v>1</v>
+      </c>
       <c r="AV58" t="inlineStr"/>
       <c r="AW58" t="inlineStr"/>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -11236,9 +11412,12 @@
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
-      <c r="AU59" t="inlineStr"/>
+      <c r="AU59" t="b">
+        <v>1</v>
+      </c>
       <c r="AV59" t="inlineStr"/>
       <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -11417,9 +11596,12 @@
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
-      <c r="AU60" t="inlineStr"/>
+      <c r="AU60" t="b">
+        <v>1</v>
+      </c>
       <c r="AV60" t="inlineStr"/>
       <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -11598,9 +11780,12 @@
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="inlineStr"/>
+      <c r="AU61" t="b">
+        <v>1</v>
+      </c>
       <c r="AV61" t="inlineStr"/>
       <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -11779,9 +11964,12 @@
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
-      <c r="AU62" t="inlineStr"/>
+      <c r="AU62" t="b">
+        <v>1</v>
+      </c>
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -11966,15 +12154,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU63" t="inlineStr">
+      <c r="AU63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV63" t="inlineStr">
         <is>
           <t>https://www.querole.net/events/3536</t>
         </is>
       </c>
-      <c r="AV63" t="n">
+      <c r="AW63" t="n">
         <v>0.95</v>
       </c>
-      <c r="AW63" t="inlineStr">
+      <c r="AX63" t="inlineStr">
         <is>
           <t>As fontes consultadas associam o Largo da Antonieta ao Bugio Centro e informam o endereço na Rua Victor Meirelles, 112, Centro, Florianópolis - SC. A evidência é consistente entre múltiplas páginas de eventos e referências ao local.</t>
         </is>
@@ -12153,9 +12344,12 @@
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
-      <c r="AU64" t="inlineStr"/>
+      <c r="AU64" t="b">
+        <v>1</v>
+      </c>
       <c r="AV64" t="inlineStr"/>
       <c r="AW64" t="inlineStr"/>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -12346,9 +12540,12 @@
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
-      <c r="AU65" t="inlineStr"/>
+      <c r="AU65" t="b">
+        <v>1</v>
+      </c>
       <c r="AV65" t="inlineStr"/>
       <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12523,15 +12720,18 @@
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
-      <c r="AU66" t="inlineStr">
+      <c r="AU66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV66" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com.br/Restaurant_Review-g303576-d33047585-Reviews-Bugio_Centro-Florianopolis_State_of_Santa_Catarina.html</t>
         </is>
       </c>
-      <c r="AV66" t="n">
+      <c r="AW66" t="n">
         <v>0.91</v>
       </c>
-      <c r="AW66" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>A busca relaciona diretamente o evento 'Samba da Antonieta' ao Bugio Centro em Florianópolis, e a página consultada informa o endereço Rua Victor Meirelles, 112. Outras fontes também associam o Samba da Antonieta ao Bugio Centro/Largo da Antonieta, reforçando a identificação do espaço no Centro de Florianópolis.</t>
         </is>
@@ -12710,9 +12910,12 @@
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
-      <c r="AU67" t="inlineStr"/>
+      <c r="AU67" t="b">
+        <v>1</v>
+      </c>
       <c r="AV67" t="inlineStr"/>
       <c r="AW67" t="inlineStr"/>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -12899,9 +13102,12 @@
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
-      <c r="AU68" t="inlineStr"/>
+      <c r="AU68" t="b">
+        <v>1</v>
+      </c>
       <c r="AV68" t="inlineStr"/>
       <c r="AW68" t="inlineStr"/>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13084,9 +13290,12 @@
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
-      <c r="AU69" t="inlineStr"/>
+      <c r="AU69" t="b">
+        <v>1</v>
+      </c>
       <c r="AV69" t="inlineStr"/>
       <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13269,9 +13478,12 @@
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
-      <c r="AU70" t="inlineStr"/>
+      <c r="AU70" t="b">
+        <v>1</v>
+      </c>
       <c r="AV70" t="inlineStr"/>
       <c r="AW70" t="inlineStr"/>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13446,9 +13658,12 @@
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
-      <c r="AU71" t="inlineStr"/>
+      <c r="AU71" t="b">
+        <v>1</v>
+      </c>
       <c r="AV71" t="inlineStr"/>
       <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13627,9 +13842,12 @@
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
-      <c r="AU72" t="inlineStr"/>
+      <c r="AU72" t="b">
+        <v>1</v>
+      </c>
       <c r="AV72" t="inlineStr"/>
       <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13812,9 +14030,12 @@
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
-      <c r="AU73" t="inlineStr"/>
+      <c r="AU73" t="b">
+        <v>1</v>
+      </c>
       <c r="AV73" t="inlineStr"/>
       <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -13997,9 +14218,12 @@
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
-      <c r="AU74" t="inlineStr"/>
+      <c r="AU74" t="b">
+        <v>1</v>
+      </c>
       <c r="AV74" t="inlineStr"/>
       <c r="AW74" t="inlineStr"/>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -14174,9 +14398,12 @@
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
-      <c r="AU75" t="inlineStr"/>
+      <c r="AU75" t="b">
+        <v>1</v>
+      </c>
       <c r="AV75" t="inlineStr"/>
       <c r="AW75" t="inlineStr"/>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14351,9 +14578,12 @@
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
-      <c r="AU76" t="inlineStr"/>
+      <c r="AU76" t="b">
+        <v>1</v>
+      </c>
       <c r="AV76" t="inlineStr"/>
       <c r="AW76" t="inlineStr"/>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -14532,15 +14762,18 @@
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
-      <c r="AU77" t="inlineStr">
+      <c r="AU77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV77" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/76706-rafa-puerta-bugio-trindade-florianopolis</t>
         </is>
       </c>
-      <c r="AV77" t="n">
+      <c r="AW77" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW77" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>A agenda do evento informa explicitamente que a apresentação ocorreu no Bugio Trindade e exibe o endereço Servidão Cristiano Vanderlei Faria, 25, Trindade, Florianópolis - SC. A mesma identificação aparece em outras fontes consultadas, reforçando a evidência.</t>
         </is>
@@ -14727,9 +14960,12 @@
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
-      <c r="AU78" t="inlineStr"/>
+      <c r="AU78" t="b">
+        <v>1</v>
+      </c>
       <c r="AV78" t="inlineStr"/>
       <c r="AW78" t="inlineStr"/>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -14904,15 +15140,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU79" t="inlineStr">
+      <c r="AU79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV79" t="inlineStr">
         <is>
           <t>https://museudasilusoes.com.br/</t>
         </is>
       </c>
-      <c r="AV79" t="n">
+      <c r="AW79" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW79" t="inlineStr">
+      <c r="AX79" t="inlineStr">
         <is>
           <t>A página oficial do Museu das Ilusões informa explicitamente a unidade em Florianópolis no Floripa Shopping, com endereço SC-401, 3116 – Saco Grande, Florianópolis – SC, e menciona o piso L3. Isso confirma o estabelecimento, o endereço e o bairro com alta confiabilidade.</t>
         </is>
@@ -15101,15 +15340,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU80" t="inlineStr">
+      <c r="AU80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV80" t="inlineStr">
         <is>
           <t>https://www.alesc.sc.gov.br/imprensa/noticia/exposicao-desdobramentos-da-transmutacao-explora-processo-de-ressignificar-vivencias/</t>
         </is>
       </c>
-      <c r="AV80" t="n">
+      <c r="AW80" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW80" t="inlineStr">
+      <c r="AX80" t="inlineStr">
         <is>
           <t>A fonte oficial da Alesc informa que a exposição ocorre na Galeria de Arte Ernesto Meyer Filho, no saguão do Palácio Barriga Verde, com endereço na Rua Dr. Jorge Luz Fontes, 310, Florianópolis. Outra página institucional da própria Alesc confirma que a galeria fica no hall do Palácio Barriga Verde, no Centro.</t>
         </is>
@@ -15282,15 +15524,18 @@
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
-      <c r="AU81" t="inlineStr">
+      <c r="AU81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV81" t="inlineStr">
         <is>
           <t>https://www.floripashopping.com.br/</t>
         </is>
       </c>
-      <c r="AV81" t="n">
+      <c r="AW81" t="n">
         <v>0.96</v>
       </c>
-      <c r="AW81" t="inlineStr">
+      <c r="AX81" t="inlineStr">
         <is>
           <t>Há evidência direta de que o Festival de Circo ocorre no Floripa Shopping e que o shopping informa seu endereço em Saco Grande. Também há material do próprio shopping indicando eventos sazonais no vão central; por isso, o espaço provável é o Floripa Shopping, na área do vão central/praça de eventos.</t>
         </is>
@@ -15469,15 +15714,18 @@
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
-      <c r="AU82" t="inlineStr">
+      <c r="AU82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV82" t="inlineStr">
         <is>
           <t>https://www.arenaopus.com/</t>
         </is>
       </c>
-      <c r="AV82" t="n">
+      <c r="AW82" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW82" t="inlineStr">
+      <c r="AX82" t="inlineStr">
         <is>
           <t>A fonte oficial da Arena Opus informa o endereço na SC-281, 4000, em Sertão do Maruim, São José/SC. Como o local informado no evento é Arena Opus, a identificação do estabelecimento é confiável.</t>
         </is>
@@ -15656,15 +15904,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU83" t="inlineStr">
+      <c r="AU83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV83" t="inlineStr">
         <is>
           <t>https://www.santacatarinadanca.com.br/</t>
         </is>
       </c>
-      <c r="AV83" t="n">
+      <c r="AW83" t="n">
         <v>0.88</v>
       </c>
-      <c r="AW83" t="inlineStr">
+      <c r="AX83" t="inlineStr">
         <is>
           <t>O evento consultado aparece com realização no Teatro Ademir Rosa, no CIC, em Florianópolis. Para o CIC/Teatro Ademir Rosa, a fonte web encontrada indica o complexo na Av. Gov. Irineu Bornhausen, 5600, no bairro Agronômica. Por isso, o nome provável do espaço é Teatro Ademir Rosa (CIC).</t>
         </is>
@@ -15845,15 +16096,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU84" t="inlineStr">
+      <c r="AU84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV84" t="inlineStr">
         <is>
           <t>https://www.cultura.sc.gov.br/programacao/2102-cineclube-escolar-da-mostra-de-cinema-infantil-de-florianopolis</t>
         </is>
       </c>
-      <c r="AV84" t="n">
+      <c r="AW84" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW84" t="inlineStr">
+      <c r="AX84" t="inlineStr">
         <is>
           <t>A fonte consultada informa que o Cineclube da Mostra de Cinema Infantil ocorre no Cinema Gilberto Gerlach, no Centro Integrado de Cultura (CIC), com endereço em Av. Gov. Irineu Bornhausen, 5600, bairro Agronômica, Florianópolis - SC.</t>
         </is>
@@ -16036,9 +16290,12 @@
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
-      <c r="AU85" t="inlineStr"/>
+      <c r="AU85" t="b">
+        <v>1</v>
+      </c>
       <c r="AV85" t="inlineStr"/>
       <c r="AW85" t="inlineStr"/>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16223,15 +16480,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU86" t="inlineStr">
+      <c r="AU86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV86" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/agenda/restaurantes</t>
         </is>
       </c>
-      <c r="AV86" t="n">
+      <c r="AW86" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW86" t="inlineStr">
+      <c r="AX86" t="inlineStr">
         <is>
           <t>Há evidência consistente de que o evento ocorreu no Centro de Eventos Oceania, também identificado como Oceania Park Hotel Spa &amp; Convention Center by RB Hotelaria, com endereço na R. do Marisco, 550, Ingleses, Florianópolis. A fonte consultada traz explicitamente o local e o endereço.</t>
         </is>
@@ -16422,9 +16682,12 @@
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
-      <c r="AU87" t="inlineStr"/>
+      <c r="AU87" t="b">
+        <v>1</v>
+      </c>
       <c r="AV87" t="inlineStr"/>
       <c r="AW87" t="inlineStr"/>
+      <c r="AX87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -16613,15 +16876,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU88" t="inlineStr">
+      <c r="AU88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV88" t="inlineStr">
         <is>
           <t>https://www.correiosc.com.br/projeto-nossa-musica-sc-da-camerata-florianopolis-sera-exibido-ao-ar-livre/</t>
         </is>
       </c>
-      <c r="AV88" t="n">
+      <c r="AW88" t="n">
         <v>0.91</v>
       </c>
-      <c r="AW88" t="inlineStr">
+      <c r="AX88" t="inlineStr">
         <is>
           <t>A evidência mais forte aponta que o evento ocorreu em frente ao Bar Bugio, no Largo da Antonieta, na Rua Victor Meirelles, Centro, Florianópolis. A fonte também identifica o Bugio Centro na Rua Victor Meirelles, 112, o que sustenta o nome provável do espaço.</t>
         </is>
@@ -16810,15 +17076,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU89" t="inlineStr">
+      <c r="AU89" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV89" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/78237-forro-de-base-delas-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AV89" t="n">
+      <c r="AW89" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW89" t="inlineStr">
+      <c r="AX89" t="inlineStr">
         <is>
           <t>O evento 'Forró de Base Delas' aparece associado ao perfil @bugiocentro e à programação da Bugio Centro, com o local explicitamente indicado como Bugio Centro e menção ao 'Largo da Antonieta' na mesma agenda. A fonte consultada informa o endereço da casa como Rua Victor Meirelles, 112 - Centro, Florianópolis - SC. Como o pedido exige apenas a identificação provável do espaço, o nome mais seguro é Bugio Centro / Largo da Antonieta, no bairro Centro.</t>
         </is>
@@ -16997,9 +17266,12 @@
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
-      <c r="AU90" t="inlineStr"/>
+      <c r="AU90" t="b">
+        <v>1</v>
+      </c>
       <c r="AV90" t="inlineStr"/>
       <c r="AW90" t="inlineStr"/>
+      <c r="AX90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -17178,9 +17450,12 @@
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
-      <c r="AU91" t="inlineStr"/>
+      <c r="AU91" t="b">
+        <v>1</v>
+      </c>
       <c r="AV91" t="inlineStr"/>
       <c r="AW91" t="inlineStr"/>
+      <c r="AX91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17359,9 +17634,12 @@
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
-      <c r="AU92" t="inlineStr"/>
+      <c r="AU92" t="b">
+        <v>1</v>
+      </c>
       <c r="AV92" t="inlineStr"/>
       <c r="AW92" t="inlineStr"/>
+      <c r="AX92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17540,9 +17818,12 @@
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
-      <c r="AU93" t="inlineStr"/>
+      <c r="AU93" t="b">
+        <v>1</v>
+      </c>
       <c r="AV93" t="inlineStr"/>
       <c r="AW93" t="inlineStr"/>
+      <c r="AX93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -17721,9 +18002,12 @@
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
-      <c r="AU94" t="inlineStr"/>
+      <c r="AU94" t="b">
+        <v>1</v>
+      </c>
       <c r="AV94" t="inlineStr"/>
       <c r="AW94" t="inlineStr"/>
+      <c r="AX94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -17902,9 +18186,12 @@
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
-      <c r="AU95" t="inlineStr"/>
+      <c r="AU95" t="b">
+        <v>1</v>
+      </c>
       <c r="AV95" t="inlineStr"/>
       <c r="AW95" t="inlineStr"/>
+      <c r="AX95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18083,15 +18370,18 @@
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
-      <c r="AU96" t="inlineStr">
+      <c r="AU96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV96" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/72270-quarteto-marimbondo-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AV96" t="n">
+      <c r="AW96" t="n">
         <v>0.96</v>
       </c>
-      <c r="AW96" t="inlineStr">
+      <c r="AX96" t="inlineStr">
         <is>
           <t>O evento associado ao perfil @bugiocentro menciona que o 'Samba da Democracia' acontece no 'Largo da Antonieta', e a página do evento identifica o local como Bugio Centro, com endereço na Rua Victor Meirelles, 112, Centro, Florianópolis. Outra fonte também relaciona o Largo da Antonieta ao Bugio Centro na Rua Victor Meirelles.</t>
         </is>
@@ -18288,15 +18578,18 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU97" t="inlineStr">
+      <c r="AU97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV97" t="inlineStr">
         <is>
           <t>https://www.baiacudealguem.com.br/pescadores-de-cultura/</t>
         </is>
       </c>
-      <c r="AV97" t="n">
+      <c r="AW97" t="n">
         <v>0.97</v>
       </c>
-      <c r="AW97" t="inlineStr">
+      <c r="AX97" t="inlineStr">
         <is>
           <t>A página oficial do Baiacu de Alguém informa explicitamente o espaço cultural e o endereço Rua Padre Lourenço R. de Andrade, 650 – Santo Antônio de Lisboa – Florianópolis (SC). Outra fonte de evento confirma o mesmo local e o bairro.</t>
         </is>
@@ -18491,15 +18784,18 @@
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
-      <c r="AU98" t="inlineStr">
+      <c r="AU98" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV98" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/servicos/comer-e-beber/bares-pubs-cerveja/bugio-centro</t>
         </is>
       </c>
-      <c r="AV98" t="n">
+      <c r="AW98" t="n">
         <v>0.95</v>
       </c>
-      <c r="AW98" t="inlineStr">
+      <c r="AX98" t="inlineStr">
         <is>
           <t xml:space="preserve">Há evidência consistente de que o espaço é o Bugio Centro, com endereço em R. Victor Meirelles, 112, no Centro de Florianópolis. A fonte consultada lista explicitamente o endereço e o bairro, compatíveis com o local informado e com referências adicionais encontradas em outras páginas. </t>
         </is>
@@ -18682,9 +18978,12 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU99" t="inlineStr"/>
+      <c r="AU99" t="b">
+        <v>1</v>
+      </c>
       <c r="AV99" t="inlineStr"/>
-      <c r="AW99" t="inlineStr">
+      <c r="AW99" t="inlineStr"/>
+      <c r="AX99" t="inlineStr">
         <is>
           <t>Não encontrei evidência confiável o bastante para associar com segurança o perfil @bugiocentro a um estabelecimento/endereço específico em Florianópolis. Os resultados recuperados não confirmam o local informado nem trazem uma identificação direta do espaço. Para evitar inventar endereço, retornei null.</t>
         </is>
@@ -18849,15 +19148,18 @@
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
-      <c r="AU100" t="inlineStr">
+      <c r="AU100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV100" t="inlineStr">
         <is>
           <t>https://devportal.pmf.sc.gov.br/entidades/cultura/index.php?noti=27706&amp;pagina=notpagina</t>
         </is>
       </c>
-      <c r="AV100" t="n">
+      <c r="AW100" t="n">
         <v>0.96</v>
       </c>
-      <c r="AW100" t="inlineStr">
+      <c r="AX100" t="inlineStr">
         <is>
           <t>A fonte da Prefeitura de Florianópolis informa explicitamente que o 1° Festival Literário e Cultural de Mulheres Escritoras ocorreu no Largo da Alfândega. Como o evento solicitado é um festival literário em Florianópolis e a evidência mais confiável encontrada aponta para esse local, o espaço provável é o Largo da Alfândega, no bairro Centro. Não encontrei evidência confiável adicional para outro endereço específico associado ao evento.</t>
         </is>
@@ -19036,9 +19338,12 @@
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
-      <c r="AU101" t="inlineStr"/>
+      <c r="AU101" t="b">
+        <v>1</v>
+      </c>
       <c r="AV101" t="inlineStr"/>
       <c r="AW101" t="inlineStr"/>
+      <c r="AX101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19217,9 +19522,12 @@
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
-      <c r="AU102" t="inlineStr"/>
+      <c r="AU102" t="b">
+        <v>1</v>
+      </c>
       <c r="AV102" t="inlineStr"/>
       <c r="AW102" t="inlineStr"/>
+      <c r="AX102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19406,9 +19714,12 @@
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
-      <c r="AU103" t="inlineStr"/>
+      <c r="AU103" t="b">
+        <v>1</v>
+      </c>
       <c r="AV103" t="inlineStr"/>
       <c r="AW103" t="inlineStr"/>
+      <c r="AX103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19595,9 +19906,12 @@
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
-      <c r="AU104" t="inlineStr"/>
+      <c r="AU104" t="b">
+        <v>1</v>
+      </c>
       <c r="AV104" t="inlineStr"/>
       <c r="AW104" t="inlineStr"/>
+      <c r="AX104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19784,9 +20098,12 @@
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
-      <c r="AU105" t="inlineStr"/>
+      <c r="AU105" t="b">
+        <v>1</v>
+      </c>
       <c r="AV105" t="inlineStr"/>
       <c r="AW105" t="inlineStr"/>
+      <c r="AX105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19973,9 +20290,12 @@
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
-      <c r="AU106" t="inlineStr"/>
+      <c r="AU106" t="b">
+        <v>1</v>
+      </c>
       <c r="AV106" t="inlineStr"/>
       <c r="AW106" t="inlineStr"/>
+      <c r="AX106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20162,9 +20482,12 @@
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
-      <c r="AU107" t="inlineStr"/>
+      <c r="AU107" t="b">
+        <v>1</v>
+      </c>
       <c r="AV107" t="inlineStr"/>
       <c r="AW107" t="inlineStr"/>
+      <c r="AX107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20351,9 +20674,12 @@
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
-      <c r="AU108" t="inlineStr"/>
+      <c r="AU108" t="b">
+        <v>1</v>
+      </c>
       <c r="AV108" t="inlineStr"/>
       <c r="AW108" t="inlineStr"/>
+      <c r="AX108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20544,9 +20870,12 @@
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
-      <c r="AU109" t="inlineStr"/>
+      <c r="AU109" t="b">
+        <v>1</v>
+      </c>
       <c r="AV109" t="inlineStr"/>
       <c r="AW109" t="inlineStr"/>
+      <c r="AX109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -20709,15 +21038,18 @@
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
-      <c r="AU110" t="inlineStr">
+      <c r="AU110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV110" t="inlineStr">
         <is>
           <t>https://www.somosaldeia.com.br/eventos/fl-1o-festival-literario-e-cultural-de-mulheres-escritoras-um-tributo-a-antonieta-de-barros</t>
         </is>
       </c>
-      <c r="AV110" t="n">
+      <c r="AW110" t="n">
         <v>0.88</v>
       </c>
-      <c r="AW110" t="inlineStr">
+      <c r="AX110" t="inlineStr">
         <is>
           <t>Encontrei evidência confiável de um festival literário em Florianópolis no Largo da Alfândega, com bairro Centro, na página do evento da Aldeia. Porém, não localizei endereço completo consistente na fonte consultada; por isso, retorno apenas o local provável e o bairro, sem inventar o endereço.</t>
         </is>
@@ -20904,15 +21236,18 @@
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
-      <c r="AU111" t="inlineStr">
+      <c r="AU111" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV111" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/servicos/comer-e-beber/o-araca-botequim.php</t>
         </is>
       </c>
-      <c r="AV111" t="n">
+      <c r="AW111" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW111" t="inlineStr">
+      <c r="AX111" t="inlineStr">
         <is>
           <t>A busca por "Samba do Araçá" em Florianópolis aponta para o perfil @oaracabotequim e para páginas que identificam o espaço como O Araçá Botequim na Lagoa da Conceição, com endereço em R. Manoel Severino de Oliveira, 19. Como há correspondência direta entre o nome do evento e o nome do estabelecimento, esta é a identificação mais provável.</t>
         </is>
@@ -21095,9 +21430,12 @@
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
-      <c r="AU112" t="inlineStr"/>
+      <c r="AU112" t="b">
+        <v>1</v>
+      </c>
       <c r="AV112" t="inlineStr"/>
       <c r="AW112" t="inlineStr"/>
+      <c r="AX112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -21272,15 +21610,18 @@
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
-      <c r="AU113" t="inlineStr">
+      <c r="AU113" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV113" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com.br/Restaurant_Review-g303576-d33047585-Reviews-Bugio_Centro-Florianopolis_State_of_Santa_Catarina.html</t>
         </is>
       </c>
-      <c r="AV113" t="n">
+      <c r="AW113" t="n">
         <v>0.86</v>
       </c>
-      <c r="AW113" t="inlineStr">
+      <c r="AX113" t="inlineStr">
         <is>
           <t>Há evidência confiável de que o local informado 'Bugio' corresponde ao Bugio Centro em Florianópolis, com endereço consistente em múltiplas fontes consultadas. Não encontrei evidência confiável indicando outro espaço mais provável para o evento da Kumba Groove.</t>
         </is>
@@ -21455,15 +21796,18 @@
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
-      <c r="AU114" t="inlineStr">
+      <c r="AU114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV114" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/servicos/comer-e-beber/bares-pubs-cerveja/bugio-centro</t>
         </is>
       </c>
-      <c r="AV114" t="n">
+      <c r="AW114" t="n">
         <v>0.98</v>
       </c>
-      <c r="AW114" t="inlineStr">
+      <c r="AX114" t="inlineStr">
         <is>
           <t>Há evidência confiável de que o “salão da Bugio” se refere ao Bugio Centro, em Florianópolis, com endereço na Rua Victor Meirelles, 112, no Centro. A fonte consultada também descreve o espaço como localizado no Centro de Florianópolis e bate com a referência ao perfil @bugiolab e ao uso de “salão” em eventos do local.</t>
         </is>
@@ -21640,15 +21984,18 @@
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
-      <c r="AU115" t="inlineStr">
+      <c r="AU115" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV115" t="inlineStr">
         <is>
           <t>https://troop.is/events/naddr1qvzqqqrukvpzp08t5xjg49jvqg77q54d5smmjastaq8d85zzuwtzdzr0m6fd0z0xqqsxxcecxgun2dp5vscnsvejxqerzwfhxvekydpsv5ursvtyxe3kvcggq9v23</t>
         </is>
       </c>
-      <c r="AV115" t="n">
+      <c r="AW115" t="n">
         <v>0.89</v>
       </c>
-      <c r="AW115" t="inlineStr">
+      <c r="AX115" t="inlineStr">
         <is>
           <t>O evento associado à mesma programação de setembro menciona 'Encontro Coletiva Linha dos Desterro — Gratuito na rua' e aponta o local como Bugic/Bugio Lab em Florianópolis. Outra fonte confirma o endereço 'R. Victor Meirelles, 112, segundo piso da Bugio Centro', e uma publicação adicional identifica 'Bugio Bar – Centro Histórico de Florianópolis (Rua Victor Meirelles, 112 – Centro – Florianópolis – SC)'. Como a referência indica que o encontro é 'na rua', o espaço provável é o entorno da Bugio Centro/Bugio Lab, no Centro.</t>
         </is>
@@ -21839,15 +22186,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU116" t="inlineStr">
+      <c r="AU116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV116" t="inlineStr">
         <is>
           <t>https://www.querole.net/events/1-Florian%C3%B3polis/2026-08-15</t>
         </is>
       </c>
-      <c r="AV116" t="n">
+      <c r="AW116" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW116" t="inlineStr">
+      <c r="AX116" t="inlineStr">
         <is>
           <t>Encontrei menções consistentes ao espaço como 'Bugio Lab' e também como 'Bugio Centro / Bugio Bar', todas associadas ao endereço 'R. Victor Meirelles, 112' em Florianópolis, com indicação explícita de 'segundo piso' em uma das fontes. O bairro aparece como Centro em fontes que vinculam esse endereço ao espaço. A evidência é convergente, embora o nome do estabelecimento varie entre Bugio Lab e Bugio Centro/Bugio Bar.</t>
         </is>
@@ -22034,15 +22384,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU117" t="inlineStr">
+      <c r="AU117" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV117" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/servicos/comer-e-beber/bares-pubs-cerveja/bugio-centro</t>
         </is>
       </c>
-      <c r="AV117" t="n">
+      <c r="AW117" t="n">
         <v>0.68</v>
       </c>
-      <c r="AW117" t="inlineStr">
+      <c r="AX117" t="inlineStr">
         <is>
           <t>Encontrei evidência confiável para o espaço Bugio no Centro de Florianópolis e para o endereço na Rua Victor Meirelles, 112. A fonte local consultada aponta o Bugio Centro em Florianópolis, e outras referências indicam o número 112 na Rua Victor Meirelles no Centro. Não achei confirmação forte e direta do nome exato 'Bugio Lab' na mesma URL, então tratei como provável correspondência do espaço e mantive o bairro como Centro.</t>
         </is>
@@ -22229,15 +22582,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU118" t="inlineStr">
+      <c r="AU118" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV118" t="inlineStr">
         <is>
           <t>https://cervejariabugio.com.br/en</t>
         </is>
       </c>
-      <c r="AV118" t="n">
+      <c r="AW118" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AW118" t="inlineStr">
+      <c r="AX118" t="inlineStr">
         <is>
           <t>O site oficial informa que o espaço fica em Florianópolis, na Rua Victor Meirelles, 112, e identifica o local como Centro Histórico. Outras fontes de apoio também associam o endereço ao bairro Centro.</t>
         </is>
@@ -22428,15 +22784,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU119" t="inlineStr">
+      <c r="AU119" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV119" t="inlineStr">
         <is>
           <t>https://secarte.ufsc.br/agenda-cultural/action~agenda/time_limit~549774000/cat_ids~58708%2C243834%2C47/request_format~html/</t>
         </is>
       </c>
-      <c r="AV119" t="n">
+      <c r="AW119" t="n">
         <v>0.89</v>
       </c>
-      <c r="AW119" t="inlineStr">
+      <c r="AX119" t="inlineStr">
         <is>
           <t>Encontrei menções consistentes ao espaço como Bugio Lab/Bugio Centro na Rua Victor Meirelles, nº 112, em Florianópolis, com indicação de Centro como bairro. A fonte consultada e outros resultados convergem para esse endereço, mas não há confirmação direta do '2º andar' na fonte principal, então mantive apenas o endereço e bairro com base no que foi evidenciado.</t>
         </is>
@@ -22615,15 +22974,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU120" t="inlineStr">
+      <c r="AU120" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV120" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/78237-forro-de-base-delas-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AV120" t="n">
+      <c r="AW120" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW120" t="inlineStr">
+      <c r="AX120" t="inlineStr">
         <is>
           <t>Há evidência consistente de que eventos de forró associados ao ecossistema Bugio em Florianópolis ocorrem no Bugio Centro/Bugio Lab. A fonte consultada informa o endereço Rua Victor Meirelles, 112 - Centro, Florianópolis - SC, e outras páginas de eventos recentes confirmam 'Bugio Lab' em Florianópolis para atividades semelhantes.</t>
         </is>
@@ -22808,15 +23170,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU121" t="inlineStr">
+      <c r="AU121" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV121" t="inlineStr">
         <is>
           <t>https://secarte.ufsc.br/agenda-cultural/action~agenda/time_limit~1718938800/cat_ids~32941%2C68191%2C58708%2C1682850%2C47/request_format~html/</t>
         </is>
       </c>
-      <c r="AV121" t="n">
+      <c r="AW121" t="n">
         <v>0.86</v>
       </c>
-      <c r="AW121" t="inlineStr">
+      <c r="AX121" t="inlineStr">
         <is>
           <t>Encontrei referência direta a 'Bugio Bar – Centro | Rua Victor Meirelles, nº112' em fonte institucional da UFSC/SeCArtE, e outra fonte menciona explicitamente 'Bugio Lab: R. Victor Meirelles, 112, segundo piso da Bugio Centro'. Isso sustenta o endereço informado e indica o bairro Centro. Não encontrei evidência confiável para um endereço diferente.</t>
         </is>
@@ -23001,15 +23366,18 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU122" t="inlineStr">
+      <c r="AU122" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV122" t="inlineStr">
         <is>
           <t>https://cervejariabugio.com.br/en</t>
         </is>
       </c>
-      <c r="AV122" t="n">
+      <c r="AW122" t="n">
         <v>0.92</v>
       </c>
-      <c r="AW122" t="inlineStr">
+      <c r="AX122" t="inlineStr">
         <is>
           <t>Encontrei evidência consistente de que o espaço fica na Rua Victor Meirelles, 112, no Centro Histórico de Florianópolis. A página oficial da Bugio informa o endereço; outra fonte de evento cita “Bugio Lab: R. Victor Meirelles, 112, segundo piso da Bugio Centro”. O bairro identificado nas fontes é Centro. Não inventei endereço além do que foi encontrado.</t>
         </is>
@@ -23192,15 +23560,18 @@
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
-      <c r="AU123" t="inlineStr">
+      <c r="AU123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV123" t="inlineStr">
         <is>
           <t>https://cervejariabugio.com.br/en</t>
         </is>
       </c>
-      <c r="AV123" t="n">
+      <c r="AW123" t="n">
         <v>0.91</v>
       </c>
-      <c r="AW123" t="inlineStr">
+      <c r="AX123" t="inlineStr">
         <is>
           <t>Encontrei fonte oficial da própria Bugio informando que o espaço 'Centro Bugio' fica na Rua Victor Meirelles, 112, Centro Histórico. Outras fontes de apoio também associam a Rua Victor Meirelles, 112 ao bairro Centro em Florianópolis. O perfil informado @bugiolab e o nome do evento apontam para esse mesmo local.</t>
         </is>
@@ -23383,9 +23754,12 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU124" t="inlineStr"/>
+      <c r="AU124" t="b">
+        <v>1</v>
+      </c>
       <c r="AV124" t="inlineStr"/>
-      <c r="AW124" t="inlineStr">
+      <c r="AW124" t="inlineStr"/>
+      <c r="AX124" t="inlineStr">
         <is>
           <t>Não encontrei evidência confiável e específica que conecte o perfil @bugiotrindade ao local do evento “Forró da Xepa” nem um endereço verificável do estabelecimento/espaço. As buscas retornaram resultados irrelevantes ou genéricos, sem confirmação do local informado. Portanto, por cautela, retorno null.</t>
         </is>

--- a/data/output/eventos_processados.xlsx
+++ b/data/output/eventos_processados.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX124"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,20 +662,25 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
+          <t>foto_url</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
           <t>publicar_webgis</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>fonte_web</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>confianca_web</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>justificativa_web</t>
         </is>
@@ -858,12 +863,13 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="b">
+        <v>1</v>
+      </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1046,18 +1052,19 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="inlineStr">
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>https://www.floripashopping.com.br/localizacao.php?lang=sp</t>
         </is>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>0.97</v>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>A fonte oficial do shopping informa a localização do Floripa Shopping em Florianópolis (SC), e uma cobertura do evento identifica o Festival de Circo de Florianópolis acontecendo na Praça de Eventos do Floripa Shopping, no endereço Rodovia SC-401, 3.116, Saco Grande, Florianópolis. Como o usuário informou apenas 'Floripa Shopping', o espaço provável é o próprio shopping; o endereço e bairro foram confirmados por fonte web confiável.</t>
         </is>
@@ -1238,18 +1245,19 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="inlineStr">
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>https://www.cultura.sc.gov.br/noticias/18496-18496-horario-de-funcionamento-dos-espacos-culturais-administrados-pela-fcc</t>
         </is>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>0.97</v>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Há evidência consistente de que o 'Cinema do CIC' corresponde ao Cinema/Sala Gilberto Gerlach no Centro Integrado de Cultura (CIC), em Florianópolis. A fonte oficial da FCC informa o CIC na Av. Gov. Irineu Bornhausen, 5600, bairro Agronômica, Florianópolis/SC.</t>
         </is>
@@ -1428,18 +1436,19 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="inlineStr">
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="inlineStr">
         <is>
           <t>https://cultura.sc.gov.br/noticias/18496-18496-horario-de-funcionamento-dos-espacos-culturais-administrados-pela-fcc</t>
         </is>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>0.95</v>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>O local informado “Teatro do CIC” corresponde ao complexo Centro Integrado de Cultura (CIC), onde fica o Teatro Ademir Rosa. A fonte consultada informa o endereço no CIC, em Florianópolis, na Avenida Governador Irineu Bornhausen, 5600, bairro Agronômica.</t>
         </is>
@@ -1618,12 +1627,13 @@
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="b">
+        <v>1</v>
+      </c>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1798,12 +1808,13 @@
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="b">
+        <v>1</v>
+      </c>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1978,12 +1989,13 @@
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="b">
+        <v>1</v>
+      </c>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2162,12 +2174,13 @@
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="b">
+        <v>1</v>
+      </c>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2352,18 +2365,19 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV10" t="inlineStr">
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW10" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/agenda/restaurantes</t>
         </is>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>A fonte consultada associa o evento "Marisco Social" ao "Centro de Eventos Oceania" e informa o endereço "R. do Marisco, 550 - Ingleses, Florianópolis"; outras fontes também reforçam "Rua do Marisco, 550, bairro Ingleses, Florianópolis/SC".</t>
         </is>
@@ -2550,18 +2564,19 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV11" t="inlineStr">
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW11" t="inlineStr">
         <is>
           <t>https://www.floripashopping.com.br/localizacao.php?lang=pt</t>
         </is>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>0.96</v>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>O site oficial do Floripa Shopping informa dois acessos/endereço no bairro Saco Grande, em Florianópolis. Como o evento foi informado apenas como ocorrendo no Floripa Shopping, esse é o local mais provável com base na fonte oficial.</t>
         </is>
@@ -2740,18 +2755,19 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="inlineStr">
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW12" t="inlineStr">
         <is>
           <t>https://www.sc.gov.br/servicos/reservar-pauta-no-teatro-ademir-rosa-cic-no-teatro-alvaro-de-carvalho-tac-e-no-teatro-pedro-ivo</t>
         </is>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>0.93</v>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>O 'Teatro do CIC' corresponde ao Teatro Ademir Rosa, que fica no Centro Integrado de Cultura (CIC). A fonte oficial do governo de SC informa o endereço e o bairro como Saco Grande para o serviço de reserva da pauta do teatro; porém outras fontes oficiais do próprio estado e da FCC situam o CIC em Avenida Governador Irineu Bornhausen, 5600, Agronômica. Como o pedido é para o local do evento e o nome informado foi genérico ('Teatro do CIC'), a identificação mais provável é o Teatro Ademir Rosa no CIC, com endereço Av. Gov. Irineu Bornhausen, 5600, Agronômica, Florianópolis.</t>
         </is>
@@ -2934,12 +2950,13 @@
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="b">
+        <v>1</v>
+      </c>
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3114,12 +3131,13 @@
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="b">
+        <v>1</v>
+      </c>
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3300,18 +3318,19 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV15" t="inlineStr">
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW15" t="inlineStr">
         <is>
           <t>https://www.sesc-sc.com.br/sescsc/conteudo/documentos/guia-de-servicos-1-semestre-2026-sesc-prainha.pdf</t>
         </is>
       </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>A fonte oficial do Sesc-SC identifica o Sesc Prainha em Florianópolis com endereço na Travessa Siryaco Atherino, 100 - Centro, e a agenda do evento informa que as atividades do 'Sesc Celebra 80 anos' ocorrem no 'Ginásio Sesc Prainha'. Como o pedido é para localizar o espaço do evento, o nome provável é Sesc Prainha e o bairro é Centro. Se desejar, posso também buscar a referência local mais próxima dentro do entorno imediato, mas sem inventar dados.</t>
         </is>
@@ -3498,12 +3517,13 @@
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="b">
+        <v>1</v>
+      </c>
       <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3682,12 +3702,17 @@
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>https://instagram.fbcn7-2.fna.fbcdn.net/v/t51.82787-15/809209376_18019298912923638_5248153458579883876_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTU3NDc3MzgzMjA3Njc4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NvEtxGmeZ00Q7kNvwHzzaLC&amp;_nc_oc=AdrIVnvkc_RquBUFsRDXxnvfCWSmKjAfPPXtoiQyJET468xGemjP-E5o7KQGgnsm9kM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbcn7-2.fna&amp;_nc_gid=3cKskU3m02P34paTgPMCzQ&amp;_nc_ss=7a22e&amp;oh=00_AQJgr83O6tTuk-Ra_jTNWIMEfPZOHj6B1NlX6AiKa2C01w&amp;oe=6AAD060F</t>
+        </is>
+      </c>
+      <c r="AV17" t="b">
+        <v>1</v>
+      </c>
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3870,18 +3895,23 @@
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/809373868_18624594913048600_1432752223229467952_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4NTU1MjM3MzEyMTc3MzU4NDE4NjI0NTk0OTA3MDQ4NjAw.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=eC2wxU0wiGEQ7kNvwFce9NC&amp;_nc_oc=AdqIsDg9vQUQtbBW0-nryAS8bJ6zxZE3R46IxdxP6rklGyLE07d_ZmC6oJQADB1WnI8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=vrRB4UAiAyEGoa8dvONqzg&amp;_nc_ss=7a22e&amp;oh=00_AQKAhYb68Fxnqqp5DijfH_8l2t00Jcr4L0le2UULiDf1-A&amp;oe=6AACE64A</t>
+        </is>
+      </c>
+      <c r="AV18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW18" t="inlineStr">
         <is>
           <t>https://cervejariabugio.com.br/?store_id=2</t>
         </is>
       </c>
-      <c r="AW18" t="n">
+      <c r="AX18" t="n">
         <v>0.96</v>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>O evento "Vozes à Solta — oficina de canto" aparece na programação do perfil @bugiocentro, e a página oficial da Cervejaria Bugio informa que o Centro Bugio fica na Rua Victor Meirelles, 112, Centro Histórico/Centro, Florianópolis. A informação é corroborada por páginas de eventos que apontam o mesmo local e endereço.</t>
         </is>
@@ -4068,12 +4098,17 @@
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>https://instagram.fsyd14-1.fna.fbcdn.net/v/t51.82787-15/807658332_18019253783923638_421651971890372082_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTM3NTYxOTIxNDUxMTYyOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjUyNy5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=gBfKK5sLPhYQ7kNvwFZkarn&amp;_nc_oc=AdpIMOkyBqmcaM1s--rRXKC95m6jegsun2DiwiLTVdDhIzfgGi82vgt4Y20kspqO2wU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd14-1.fna&amp;_nc_gid=DgGqhEwqegfDM9zhfgMMXw&amp;_nc_ss=7a22e&amp;oh=00_AQLnaA717Ln2ILrcKc-kH4dQDyZ85uWMpiDMUjqU_eYpKA&amp;oe=6AAD1331</t>
+        </is>
+      </c>
+      <c r="AV19" t="b">
+        <v>1</v>
+      </c>
       <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4256,12 +4291,17 @@
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>https://instagram.fsyd14-1.fna.fbcdn.net/v/t51.82787-15/807658332_18019253783923638_421651971890372082_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTM3NTYxOTIxNDUxMTYyOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjUyNy5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=gBfKK5sLPhYQ7kNvwFZkarn&amp;_nc_oc=AdpIMOkyBqmcaM1s--rRXKC95m6jegsun2DiwiLTVdDhIzfgGi82vgt4Y20kspqO2wU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd14-1.fna&amp;_nc_gid=DgGqhEwqegfDM9zhfgMMXw&amp;_nc_ss=7a22e&amp;oh=00_AQLnaA717Ln2ILrcKc-kH4dQDyZ85uWMpiDMUjqU_eYpKA&amp;oe=6AAD1331</t>
+        </is>
+      </c>
+      <c r="AV20" t="b">
+        <v>1</v>
+      </c>
       <c r="AW20" t="inlineStr"/>
       <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4444,12 +4484,17 @@
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>https://instagram.fsyd14-1.fna.fbcdn.net/v/t51.82787-15/807658332_18019253783923638_421651971890372082_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTM3NTYxOTIxNDUxMTYyOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjUyNy5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=gBfKK5sLPhYQ7kNvwFZkarn&amp;_nc_oc=AdpIMOkyBqmcaM1s--rRXKC95m6jegsun2DiwiLTVdDhIzfgGi82vgt4Y20kspqO2wU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd14-1.fna&amp;_nc_gid=DgGqhEwqegfDM9zhfgMMXw&amp;_nc_ss=7a22e&amp;oh=00_AQLnaA717Ln2ILrcKc-kH4dQDyZ85uWMpiDMUjqU_eYpKA&amp;oe=6AAD1331</t>
+        </is>
+      </c>
+      <c r="AV21" t="b">
+        <v>1</v>
+      </c>
       <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4628,12 +4673,17 @@
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>https://instagram.fsyd14-1.fna.fbcdn.net/v/t51.82787-15/807658332_18019253783923638_421651971890372082_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTM3NTYxOTIxNDUxMTYyOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjUyNy5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=gBfKK5sLPhYQ7kNvwFZkarn&amp;_nc_oc=AdpIMOkyBqmcaM1s--rRXKC95m6jegsun2DiwiLTVdDhIzfgGi82vgt4Y20kspqO2wU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd14-1.fna&amp;_nc_gid=DgGqhEwqegfDM9zhfgMMXw&amp;_nc_ss=7a22e&amp;oh=00_AQLnaA717Ln2ILrcKc-kH4dQDyZ85uWMpiDMUjqU_eYpKA&amp;oe=6AAD1331</t>
+        </is>
+      </c>
+      <c r="AV22" t="b">
+        <v>1</v>
+      </c>
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4816,12 +4866,17 @@
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>https://instagram.fsyd14-1.fna.fbcdn.net/v/t51.82787-15/807658332_18019253783923638_421651971890372082_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4NTM3NTYxOTIxNDUxMTYyOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjUyNy5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=gBfKK5sLPhYQ7kNvwFZkarn&amp;_nc_oc=AdpIMOkyBqmcaM1s--rRXKC95m6jegsun2DiwiLTVdDhIzfgGi82vgt4Y20kspqO2wU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd14-1.fna&amp;_nc_gid=DgGqhEwqegfDM9zhfgMMXw&amp;_nc_ss=7a22e&amp;oh=00_AQLnaA717Ln2ILrcKc-kH4dQDyZ85uWMpiDMUjqU_eYpKA&amp;oe=6AAD1331</t>
+        </is>
+      </c>
+      <c r="AV23" t="b">
+        <v>1</v>
+      </c>
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5000,18 +5055,23 @@
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV24" t="inlineStr">
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel16-1.fna.fbcdn.net/v/t51.82787-15/806366147_18475041718115878_6134736690846412796_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4NTM1Njk2NTU0OTQ5OTc3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI4NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K_DBPe8JMiIQ7kNvwF9ZzQr&amp;_nc_oc=AdpHpteFEdNYvAq1rqUbteLDJBDnoc5dHkHyMdYFIDNAsVq1MhdsYsbOaGL1rbLqsYQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel16-1.fna&amp;_nc_gid=BkeVGxrOfIJmR3w9zOQdwA&amp;_nc_ss=7a22e&amp;oh=00_AQJyaPoe31jHz3P4fOeJqsuSOaFYqy_MJ3JrD3nKI6nPhQ&amp;oe=6AACF4E6</t>
+        </is>
+      </c>
+      <c r="AV24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW24" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/72270-quarteto-marimbondo-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AW24" t="n">
+      <c r="AX24" t="n">
         <v>0.96</v>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>Há evidência direta de que o evento “Vinilaria Bugio” ocorre no Bugio Centro, com endereço R. Victor Meirelles, 112, no bairro Centro, Florianópolis. A fonte também relaciona o perfil @bugiocentro ao local do evento. Como há correspondência explícita entre o evento e o espaço, a confiança é alta.</t>
         </is>
@@ -5188,18 +5248,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>https://instagram.fadl7-2.fna.fbcdn.net/v/t51.82787-15/807750539_17954605317250034_695833447136362993_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NDkxNzgzODk2NTI2MDA3OTE3OTU0NjA1MzE0MjUwMDM0.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEyODQuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=dhp9TjCUsKIQ7kNvwEBeu_z&amp;_nc_oc=AdqKosDAdjNGe7xXohUSp-1RAQOCZF941UEZHZuJFJxxyBOLtffVTBa55UUVjbzULPE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl7-2.fna&amp;_nc_gid=6Tp7GYKMlgh5XDOUYtW8nA&amp;_nc_ss=7a22e&amp;oh=00_AQJ_QZbZyDVfbD3tycxkeNh1mreSkfk7Aedw_o8hznXffQ&amp;oe=6AACFF1A</t>
+        </is>
+      </c>
+      <c r="AV25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW25" t="inlineStr">
         <is>
           <t>https://www.cervejariabugio.com.br/</t>
         </is>
       </c>
-      <c r="AW25" t="n">
+      <c r="AX25" t="n">
         <v>0.76</v>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>O perfil @bugiolab e as buscas retornaram evidências para "Bugio"/"Bugio Lab" em Florianópolis; o site oficial da Cervejaria Bugio informa que o Centro Bugio fica no centro histórico de Florianópolis, na esquina da rua Victor Meirelles com a Nunes Machado. Não encontrei uma página oficial separada que confirme o nome exatamente como "bugiolab", então a identificação é provável, não absoluta.</t>
         </is>
@@ -5374,12 +5439,17 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>https://instagram.fadl7-2.fna.fbcdn.net/v/t51.82787-15/807750539_17954605317250034_695833447136362993_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NDkxNzgzODk2NTI2MDA3OTE3OTU0NjA1MzE0MjUwMDM0.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEyODQuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=dhp9TjCUsKIQ7kNvwEBeu_z&amp;_nc_oc=AdqKosDAdjNGe7xXohUSp-1RAQOCZF941UEZHZuJFJxxyBOLtffVTBa55UUVjbzULPE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl7-2.fna&amp;_nc_gid=6Tp7GYKMlgh5XDOUYtW8nA&amp;_nc_ss=7a22e&amp;oh=00_AQJ_QZbZyDVfbD3tycxkeNh1mreSkfk7Aedw_o8hznXffQ&amp;oe=6AACFF1A</t>
+        </is>
+      </c>
+      <c r="AV26" t="b">
+        <v>1</v>
+      </c>
       <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr">
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Não encontrei evidência confiável que vincule “bugiolab” a um estabelecimento específico em Florianópolis. As buscas retornaram resultados não relacionados ou insuficientes para confirmar nome, endereço e bairro sem inventar informações.</t>
         </is>
@@ -5554,12 +5624,17 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>https://instagram.fadl7-2.fna.fbcdn.net/v/t51.82787-15/807750539_17954605317250034_695833447136362993_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NDkxNzgzODk2NTI2MDA3OTE3OTU0NjA1MzE0MjUwMDM0.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEyODQuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=dhp9TjCUsKIQ7kNvwEBeu_z&amp;_nc_oc=AdqKosDAdjNGe7xXohUSp-1RAQOCZF941UEZHZuJFJxxyBOLtffVTBa55UUVjbzULPE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl7-2.fna&amp;_nc_gid=6Tp7GYKMlgh5XDOUYtW8nA&amp;_nc_ss=7a22e&amp;oh=00_AQJ_QZbZyDVfbD3tycxkeNh1mreSkfk7Aedw_o8hznXffQ&amp;oe=6AACFF1A</t>
+        </is>
+      </c>
+      <c r="AV27" t="b">
+        <v>1</v>
+      </c>
       <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr">
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Não encontrei evidência confiável que conecte explicitamente o perfil @bugiolab ao local do evento em Florianópolis. As buscas retornaram resultados genéricos de Google Maps sem confirmação do estabelecimento/espaco correspondente a 'bugiolab'. Para não inventar endereço ou bairro, retorno null.</t>
         </is>
@@ -5742,18 +5817,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV28" t="inlineStr">
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>https://instagram.fadl7-2.fna.fbcdn.net/v/t51.82787-15/807750539_17954605317250034_695833447136362993_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NDkxNzgzODk2NTI2MDA3OTE3OTU0NjA1MzE0MjUwMDM0.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEyODQuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=dhp9TjCUsKIQ7kNvwEBeu_z&amp;_nc_oc=AdqKosDAdjNGe7xXohUSp-1RAQOCZF941UEZHZuJFJxxyBOLtffVTBa55UUVjbzULPE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl7-2.fna&amp;_nc_gid=6Tp7GYKMlgh5XDOUYtW8nA&amp;_nc_ss=7a22e&amp;oh=00_AQJ_QZbZyDVfbD3tycxkeNh1mreSkfk7Aedw_o8hznXffQ&amp;oe=6AACFF1A</t>
+        </is>
+      </c>
+      <c r="AV28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW28" t="inlineStr">
         <is>
           <t>https://www.cervejariabugio.com.br/</t>
         </is>
       </c>
-      <c r="AW28" t="n">
+      <c r="AX28" t="n">
         <v>0.96</v>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AY28" t="inlineStr">
         <is>
           <t>O site oficial informa que o “Centro Bugio” fica no centro histórico de Florianópolis e traz o endereço “Rua Victor Meirelles, 112, Centro Histórico”. Isso corresponde ao local provável do evento associado ao perfil @bugiolab.</t>
         </is>
@@ -5862,12 +5942,17 @@
           <t>Local não encontrado na HERE nem na pesquisa web</t>
         </is>
       </c>
-      <c r="AU29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/808192294_18103122734620922_6956852689869804096_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4NDc1OTcyNTI4OTU2Njc4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=qGQPpVePlQ0Q7kNvwHB5JBw&amp;_nc_oc=AdoNfbJra3HEUF2nRNJUiLmrlCJWGi4ATZu5xHR4In26EmhkjESYsfwYholmEYiuFOw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=relNu8NRt_kk2hMwlV7muQ&amp;_nc_ss=7a22e&amp;oh=00_AQIam7aGv3EEtzby0Q46hs26RJ7WhlfALL6w5LA-xLuqjQ&amp;oe=6AACEB68</t>
+        </is>
+      </c>
+      <c r="AV29" t="b">
+        <v>1</v>
+      </c>
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5972,12 +6057,17 @@
           <t>Local não encontrado na HERE nem na pesquisa web</t>
         </is>
       </c>
-      <c r="AU30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg4-2.cdninstagram.com/v/t51.82787-15/793902356_18103113101620922_6635615926362002055_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4NDcwOTczMzY1ODg1NDQ2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYwMC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LwZuW4BiX6AQ7kNvwEN-9K0&amp;_nc_oc=AdoGd6KBwBr8NRD-2GJcGGIuZWuH2DCA4qZI1p27Pcb1mVC9OSIt7cXl4h_TUz3gYnE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_gid=Y35Mfw3eq0VYKVwu9pdMRQ&amp;_nc_ss=7a22e&amp;oh=00_AQKvuu7jcwIlDSoCiAZKoTkmnKBrYsb4bmL7-vL7G1ARbA&amp;oe=6AACDF83</t>
+        </is>
+      </c>
+      <c r="AV30" t="b">
+        <v>1</v>
+      </c>
       <c r="AW30" t="inlineStr"/>
       <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6160,12 +6250,17 @@
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/805833705_17902241193579813_6328492597128564353_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4NDY4Mjg5OTA3MTM4NDAwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ek5Z9zpGMfgQ7kNvwG249Tp&amp;_nc_oc=AdrYLXIGUkXk5zOetqFUosBEv2pj0MR1a4Rds4VWxMJz0FO_GasHxEEq8wHkh-Ozp-c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=4TyB6IjnPEPywV7OD4Sguw&amp;_nc_ss=7a22e&amp;oh=00_AQJCICLUxVwXaFtmTvsQD0PdsSjocq_HctOycyAR0Bf_JA&amp;oe=6AAD02E0</t>
+        </is>
+      </c>
+      <c r="AV31" t="b">
+        <v>1</v>
+      </c>
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6340,18 +6435,23 @@
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV32" t="inlineStr">
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/806491473_18019088333923638_2372785123610067930_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4NDU0ODIwOTk1MzU2MzA1MDE4MDE5MDg4MzMwOTIzNjM4.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEyODQuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=CpqZbXfo90MQ7kNvwFaI1D6&amp;_nc_oc=AdqdNK2i-cjRiNE1e10tuiMg8yatgoEwdX73RrWNs6FvjZ_gdv46NHvtOOsf3EQ9jqw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=KhNmRrXDlj6gXfz0p6bWew&amp;_nc_ss=7a22e&amp;oh=00_AQKUEXKr-vydULaLLOFq-w7OjRtBZgArFjkF237tW5lNiA&amp;oe=6AACEA89</t>
+        </is>
+      </c>
+      <c r="AV32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW32" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/76708-forro-da-nati-bugio-trindade-florianopolis</t>
         </is>
       </c>
-      <c r="AW32" t="n">
+      <c r="AX32" t="n">
         <v>0.95</v>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>O evento "Forró da Nati + chope em dobro" aparece associado ao perfil @bugiotrindade e à casa "Bugio Trindade". A fonte consultada informa explicitamente o endereço completo e o bairro Trindade, em Florianópolis.</t>
         </is>
@@ -6538,12 +6638,17 @@
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/806176946_18474817402115878_1066020849190318838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NDU0MTU2NjgzMTgwNDM2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI4NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S68e7H2lDX8Q7kNvwFZDK0F&amp;_nc_oc=AdqU0ng7qd95uhfIoW6o-F1qqQ0PV7Q-WrzMJQzVOfQfZTJ-Ylx6NJrfwgbZiRLY1No&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=LyCoCO88lHYwl2-mwXB-ow&amp;_nc_ss=7a22e&amp;oh=00_AQIlcoyFlpFH7GTxN7hJRXzTpLsIzMWDpHo0vBOxbdNi8A&amp;oe=6AACF9AC</t>
+        </is>
+      </c>
+      <c r="AV33" t="b">
+        <v>1</v>
+      </c>
       <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6726,18 +6831,23 @@
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV34" t="inlineStr">
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/806176946_18474817402115878_1066020849190318838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NDU0MTU2NjgzMTgwNDM2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI4NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S68e7H2lDX8Q7kNvwFZDK0F&amp;_nc_oc=AdqU0ng7qd95uhfIoW6o-F1qqQ0PV7Q-WrzMJQzVOfQfZTJ-Ylx6NJrfwgbZiRLY1No&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=LyCoCO88lHYwl2-mwXB-ow&amp;_nc_ss=7a22e&amp;oh=00_AQIlcoyFlpFH7GTxN7hJRXzTpLsIzMWDpHo0vBOxbdNi8A&amp;oe=6AACF9AC</t>
+        </is>
+      </c>
+      <c r="AV34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW34" t="inlineStr">
         <is>
           <t>https://www.vaidancar.com.br/baile/details/BLDVzNETPy</t>
         </is>
       </c>
-      <c r="AW34" t="n">
+      <c r="AX34" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>O evento "Trio Sambachoro" aparece associado ao Bugio Centro, com a localização explicitada em Rua Victor Meirelles, 112, Centro, Florianópolis - SC. A menção ao "Largo da Antonieta" nos eventos do mesmo perfil reforça que o espaço fica nessa área do Centro de Florianópolis.</t>
         </is>
@@ -6922,18 +7032,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV35" t="inlineStr">
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/806176946_18474817402115878_1066020849190318838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NDU0MTU2NjgzMTgwNDM2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI4NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S68e7H2lDX8Q7kNvwFZDK0F&amp;_nc_oc=AdqU0ng7qd95uhfIoW6o-F1qqQ0PV7Q-WrzMJQzVOfQfZTJ-Ylx6NJrfwgbZiRLY1No&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=LyCoCO88lHYwl2-mwXB-ow&amp;_nc_ss=7a22e&amp;oh=00_AQIlcoyFlpFH7GTxN7hJRXzTpLsIzMWDpHo0vBOxbdNi8A&amp;oe=6AACF9AC</t>
+        </is>
+      </c>
+      <c r="AV35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW35" t="inlineStr">
         <is>
           <t>https://www.cervejariabugio.com.br/ ; https://troop.is/events/naddr1qvzqqqrukvpzp08t5xjg49jvqg77q54d5smmjastaq8d85zzuwtzdzr0m6fd0z0xqqsxxcecxgun2dp5vscnsvejxqerzwfhxvekydpsv5ursvtyxe3kvcggq9v23 ; https://www.tripadvisor.com.br/Restaurant_Review-g303576-d33047585-Reviews-Bugio_Centro-Florianopolis_State_of_Santa_Catarina.html</t>
         </is>
       </c>
-      <c r="AW35" t="n">
+      <c r="AX35" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AY35" t="inlineStr">
         <is>
           <t>Encontrei evidência de que o Bugio Lab fica no Bugio Centro, em Florianópolis, no endereço Rua Victor Meirelles, 112, segundo piso; outras fontes reforçam o mesmo endereço para Bugio Centro e situam o estabelecimento no bairro Centro. A identificação do nome 'Bugio Lab' como espaço ligado ao Bugio Centro é consistente com as fontes encontradas. Nenhuma fonte confiável indicou outro endereço.</t>
         </is>
@@ -7120,12 +7235,17 @@
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/806176946_18474817402115878_1066020849190318838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NDU0MTU2NjgzMTgwNDM2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI4NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S68e7H2lDX8Q7kNvwFZDK0F&amp;_nc_oc=AdqU0ng7qd95uhfIoW6o-F1qqQ0PV7Q-WrzMJQzVOfQfZTJ-Ylx6NJrfwgbZiRLY1No&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=LyCoCO88lHYwl2-mwXB-ow&amp;_nc_ss=7a22e&amp;oh=00_AQIlcoyFlpFH7GTxN7hJRXzTpLsIzMWDpHo0vBOxbdNi8A&amp;oe=6AACF9AC</t>
+        </is>
+      </c>
+      <c r="AV36" t="b">
+        <v>1</v>
+      </c>
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7304,12 +7424,17 @@
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/806176946_18474817402115878_1066020849190318838_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4NDU0MTU2NjgzMTgwNDM2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI4NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S68e7H2lDX8Q7kNvwFZDK0F&amp;_nc_oc=AdqU0ng7qd95uhfIoW6o-F1qqQ0PV7Q-WrzMJQzVOfQfZTJ-Ylx6NJrfwgbZiRLY1No&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=LyCoCO88lHYwl2-mwXB-ow&amp;_nc_ss=7a22e&amp;oh=00_AQIlcoyFlpFH7GTxN7hJRXzTpLsIzMWDpHo0vBOxbdNi8A&amp;oe=6AACF9AC</t>
+        </is>
+      </c>
+      <c r="AV37" t="b">
+        <v>1</v>
+      </c>
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7506,18 +7631,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV38" t="inlineStr">
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t51.82787-15/806093247_18102994937620922_265530640879859862_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4NDEyMDkxNTU4NTM1MTk1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=eJZHZSIdiRMQ7kNvwFNxQQB&amp;_nc_oc=AdqJb93ngH3xv3seeeA0s-sydnjwKFDJH2XY5x0kysNuT6msuge8w51H126eUQ900yDFc8hAXrHU7z7bQzXgRAVR&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=BKE5L2dYGXKwdZ4KsFjd_Q&amp;_nc_ss=7a22e&amp;oh=00_AQL35Ldvq5LZTuXRG1Li7-cq9_v_qCx7wwBY5FRLLrd5ZQ&amp;oe=6AAD0293</t>
+        </is>
+      </c>
+      <c r="AV38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW38" t="inlineStr">
         <is>
           <t>https://www.baiacudealguem.com.br/category/associacao-cultural/</t>
         </is>
       </c>
-      <c r="AW38" t="n">
+      <c r="AX38" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>A página oficial da Associação Cultural Baiacu de Alguém informa o endereço completo da sede como Rua Padre Lourenço R. de Andrade, 650 – Santo Antônio de Lisboa – Florianópolis (SC), confirmando o local informado do evento.</t>
         </is>
@@ -7708,12 +7838,17 @@
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t51.82787-15/804647439_18280965682290806_7996666812588991539_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NDEwODA5NDM3NTYzOTkxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NBXJlUopg6kQ7kNvwGmLuaa&amp;_nc_oc=Adr0kugK8znF37hed-c3Mgye7kK1cUdt1ZsvUG6rsuAZ5CYDeTHd2I4h5nrU-Da3RwrPU5FDjRl_T4Wl5J3Zk8bu&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=kA6cbzOBC8X8xMT22NsNwQ&amp;_nc_ss=7a22e&amp;oh=00_AQJ8-MFEXdAlun6SRGrIS2T3qGVLi4L4L7ZN26lC0N6k7A&amp;oe=6AACF513</t>
+        </is>
+      </c>
+      <c r="AV39" t="b">
+        <v>1</v>
+      </c>
       <c r="AW39" t="inlineStr"/>
       <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7904,12 +8039,17 @@
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
-      <c r="AU40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t51.82787-15/804647439_18280965682290806_7996666812588991539_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NDEwODA5NDM3NTYzOTkxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NBXJlUopg6kQ7kNvwGmLuaa&amp;_nc_oc=Adr0kugK8znF37hed-c3Mgye7kK1cUdt1ZsvUG6rsuAZ5CYDeTHd2I4h5nrU-Da3RwrPU5FDjRl_T4Wl5J3Zk8bu&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=kA6cbzOBC8X8xMT22NsNwQ&amp;_nc_ss=7a22e&amp;oh=00_AQJ8-MFEXdAlun6SRGrIS2T3qGVLi4L4L7ZN26lC0N6k7A&amp;oe=6AACF513</t>
+        </is>
+      </c>
+      <c r="AV40" t="b">
+        <v>1</v>
+      </c>
       <c r="AW40" t="inlineStr"/>
       <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8096,12 +8236,17 @@
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t51.82787-15/804647439_18280965682290806_7996666812588991539_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NDEwODA5NDM3NTYzOTkxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NBXJlUopg6kQ7kNvwGmLuaa&amp;_nc_oc=Adr0kugK8znF37hed-c3Mgye7kK1cUdt1ZsvUG6rsuAZ5CYDeTHd2I4h5nrU-Da3RwrPU5FDjRl_T4Wl5J3Zk8bu&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=kA6cbzOBC8X8xMT22NsNwQ&amp;_nc_ss=7a22e&amp;oh=00_AQJ8-MFEXdAlun6SRGrIS2T3qGVLi4L4L7ZN26lC0N6k7A&amp;oe=6AACF513</t>
+        </is>
+      </c>
+      <c r="AV41" t="b">
+        <v>1</v>
+      </c>
       <c r="AW41" t="inlineStr"/>
       <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8288,12 +8433,17 @@
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
-      <c r="AU42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t51.82787-15/804647439_18280965682290806_7996666812588991539_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4NDEwODA5NDM3NTYzOTkxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NBXJlUopg6kQ7kNvwGmLuaa&amp;_nc_oc=Adr0kugK8znF37hed-c3Mgye7kK1cUdt1ZsvUG6rsuAZ5CYDeTHd2I4h5nrU-Da3RwrPU5FDjRl_T4Wl5J3Zk8bu&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=kA6cbzOBC8X8xMT22NsNwQ&amp;_nc_ss=7a22e&amp;oh=00_AQJ8-MFEXdAlun6SRGrIS2T3qGVLi4L4L7ZN26lC0N6k7A&amp;oe=6AACF513</t>
+        </is>
+      </c>
+      <c r="AV42" t="b">
+        <v>1</v>
+      </c>
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8468,18 +8618,23 @@
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
-      <c r="AU43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV43" t="inlineStr">
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>https://instagram.fjdo1-2.fna.fbcdn.net/v/t51.82787-15/805783903_18328918468277782_237081791223379053_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4Mzk5Nzc1ODgxMzIyNjYyNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzA3Mi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=pMiMt-RxpREQ7kNvwE4xHNw&amp;_nc_oc=AdoMgUh9NhA0znHAOZHtNqpOHrgHe5h_XjQnY0NSt8DuwGMXy1GDLVCl3h6265qyX2A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fjdo1-2.fna&amp;_nc_gid=4yIQD-Ta71Ns40rpxJLCPw&amp;_nc_ss=7a22e&amp;oh=00_AQKkMheoeUCVRDWsucpFpjWvk4DyoK0TwvfuZfwWzMzB-Q&amp;oe=6AACE6D8</t>
+        </is>
+      </c>
+      <c r="AV43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW43" t="inlineStr">
         <is>
           <t>https://fundacaoculturalbadesc.com/</t>
         </is>
       </c>
-      <c r="AW43" t="n">
+      <c r="AX43" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX43" t="inlineStr">
+      <c r="AY43" t="inlineStr">
         <is>
           <t>A página oficial da Fundação Cultural Badesc informa que a instituição fica na Rua Visconde de Ouro Preto, 216, Centro, Florianópolis/SC, e o conteúdo sobre a exposição 'Ressonâncias do Gesto' indica que ela ocupa o Espaço 3 da própria Fundação. A evidência é consistente e direta, por isso o espaço provável é a Fundação Cultural Badesc, no bairro Centro.</t>
         </is>
@@ -8672,18 +8827,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV44" t="inlineStr">
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806101214_18121555975909973_645963112674512149_n.webp?_nc_cat=108&amp;ig_cache_key=Mzk4NDA1NzgzMjYwNzEyOTIyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=g84S-abKo0wQ7kNvwFcO1LN&amp;_nc_oc=Adoz1GCZ7HspAJ5RbZQzD4A48Yq16yITug7Ir1GEyUm2svJYd-f_gJYJs-kQJuuXEZ4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=sSZaTVgBJnTsolvbvDCz0A&amp;_nc_ss=7a22e&amp;oh=00_AQLvEYWz4E9L7MDmgGroagvQD5Mq-gDj5KyYKBU8_9BDQQ&amp;oe=6AACE2B8</t>
+        </is>
+      </c>
+      <c r="AV44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW44" t="inlineStr">
         <is>
           <t>https://www.cylex.com.br/florianopolis/associa%C3%A7%C3%A3o-cultural-baiacu-de-alguem-11871181.html</t>
         </is>
       </c>
-      <c r="AW44" t="n">
+      <c r="AX44" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX44" t="inlineStr">
+      <c r="AY44" t="inlineStr">
         <is>
           <t>Encontrei uma listagem do estabelecimento em Florianópolis com o nome Associação Cultural Baiacu de Alguem/Baiacu de Alguém, no endereço Rua Pe Lourenço R. de Andrade 650, 88050-400, em Santo Antônio de Lisboa. A informação é consistente com outras referências encontradas para o Baiacu de Alguém em Santo Antônio de Lisboa, mas a fonte direta do endereço é a listagem consultada.</t>
         </is>
@@ -8868,18 +9028,23 @@
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV45" t="inlineStr">
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>https://scontent-mxp1-1.cdninstagram.com/v/t51.82787-15/806101214_18121555975909973_645963112674512149_n.webp?_nc_cat=108&amp;ig_cache_key=Mzk4NDA1NzgzMjYwNzEyOTIyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=g84S-abKo0wQ7kNvwFcO1LN&amp;_nc_oc=Adoz1GCZ7HspAJ5RbZQzD4A48Yq16yITug7Ir1GEyUm2svJYd-f_gJYJs-kQJuuXEZ4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp1-1.cdninstagram.com&amp;_nc_gid=sSZaTVgBJnTsolvbvDCz0A&amp;_nc_ss=7a22e&amp;oh=00_AQLvEYWz4E9L7MDmgGroagvQD5Mq-gDj5KyYKBU8_9BDQQ&amp;oe=6AACE2B8</t>
+        </is>
+      </c>
+      <c r="AV45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW45" t="inlineStr">
         <is>
           <t>https://www.baiacudealguem.com.br/pescadores-de-cultura/</t>
         </is>
       </c>
-      <c r="AW45" t="n">
+      <c r="AX45" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AY45" t="inlineStr">
         <is>
           <t>A fonte oficial do coletivo/associação Baiacu de Alguém informa explicitamente o endereço Rua Padre Lourenço R. de Andrade, 650 – Santo Antônio de Lisboa – Florianópolis (SC). Outras fontes consultadas reforçam o mesmo local como 'Espaço Cultural Baiacu de Alguém' no bairro Santo Antônio de Lisboa. Como você pediu para não inventar endereço, usei apenas o que aparece com evidência convergente na web.</t>
         </is>
@@ -9058,12 +9223,17 @@
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
-      <c r="AU46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>https://scontent-ord5-2.cdninstagram.com/v/t51.82787-15/803067906_18328906204277782_8002973811608322765_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4Mzk0NjE5NTUwMjkyOTg3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m4VojJtg9skQ7kNvwHlMBDJ&amp;_nc_oc=AdrXc8m7KEnz4ojLUi80CmCEYtOPV5YjfRPjZ67-kM5ib3GhqX_lhwrsOuNQafxhAIM9m4j-9katbLVr3aqI_AdD&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=lV4Z46huQPE2uVmxwXYsYQ&amp;_nc_ss=7a22e&amp;oh=00_AQI4Krw2CGt36KI8c20yT4ZuqToR-8h_gDIy87eHpAoSDg&amp;oe=6AACF7D8</t>
+        </is>
+      </c>
+      <c r="AV46" t="b">
+        <v>1</v>
+      </c>
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9238,12 +9408,17 @@
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/805119819_18474649414115878_3601475395675608769_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4MzkwNzYyMjE5MTQ1NDgzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uFX7iLcALa0Q7kNvwHw2pQJ&amp;_nc_oc=Adr1AM4W6nrBHqEDZb1Rd6CHXoaas8AK_K0djVIppxcS5voe1EWQwNV0EvHKVnIMWHM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=ys-wVeJeKGVma3L5g6syHw&amp;_nc_ss=7a22e&amp;oh=00_AQKA7e0JSt9kySIYhyPAQDeSA7VSVTcWNiZ4ZbnfFlFZhw&amp;oe=6AAD12BB</t>
+        </is>
+      </c>
+      <c r="AV47" t="b">
+        <v>1</v>
+      </c>
       <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9424,18 +9599,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV48" t="inlineStr">
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/805119819_18474649414115878_3601475395675608769_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4MzkwNzYyMjE5MTQ1NDgzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uFX7iLcALa0Q7kNvwHw2pQJ&amp;_nc_oc=Adr1AM4W6nrBHqEDZb1Rd6CHXoaas8AK_K0djVIppxcS5voe1EWQwNV0EvHKVnIMWHM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=ys-wVeJeKGVma3L5g6syHw&amp;_nc_ss=7a22e&amp;oh=00_AQKA7e0JSt9kySIYhyPAQDeSA7VSVTcWNiZ4ZbnfFlFZhw&amp;oe=6AAD12BB</t>
+        </is>
+      </c>
+      <c r="AV48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW48" t="inlineStr">
         <is>
           <t>https://www.vaidancar.com.br/baile/details/BLDVzNETPy</t>
         </is>
       </c>
-      <c r="AW48" t="n">
+      <c r="AX48" t="n">
         <v>0.91</v>
       </c>
-      <c r="AX48" t="inlineStr">
+      <c r="AY48" t="inlineStr">
         <is>
           <t xml:space="preserve">O evento 'Trio Sambachoro' aparece associado ao Bugio Centro, com localização explicitada como Rua Victor Meirelles, 112, Centro - Florianópolis - SC. Outras fontes sobre o Largo da Antonieta situam o espaço no Centro-Leste de Florianópolis, entre as ruas Vítor Meirelles e Nunes Machado, reforçando a identificação do local. </t>
         </is>
@@ -9622,12 +9802,17 @@
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
-      <c r="AU49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/805119819_18474649414115878_3601475395675608769_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4MzkwNzYyMjE5MTQ1NDgzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uFX7iLcALa0Q7kNvwHw2pQJ&amp;_nc_oc=Adr1AM4W6nrBHqEDZb1Rd6CHXoaas8AK_K0djVIppxcS5voe1EWQwNV0EvHKVnIMWHM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=ys-wVeJeKGVma3L5g6syHw&amp;_nc_ss=7a22e&amp;oh=00_AQKA7e0JSt9kySIYhyPAQDeSA7VSVTcWNiZ4ZbnfFlFZhw&amp;oe=6AAD12BB</t>
+        </is>
+      </c>
+      <c r="AV49" t="b">
+        <v>1</v>
+      </c>
       <c r="AW49" t="inlineStr"/>
       <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9806,12 +9991,17 @@
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/805119819_18474649414115878_3601475395675608769_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4MzkwNzYyMjE5MTQ1NDgzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uFX7iLcALa0Q7kNvwHw2pQJ&amp;_nc_oc=Adr1AM4W6nrBHqEDZb1Rd6CHXoaas8AK_K0djVIppxcS5voe1EWQwNV0EvHKVnIMWHM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=ys-wVeJeKGVma3L5g6syHw&amp;_nc_ss=7a22e&amp;oh=00_AQKA7e0JSt9kySIYhyPAQDeSA7VSVTcWNiZ4ZbnfFlFZhw&amp;oe=6AAD12BB</t>
+        </is>
+      </c>
+      <c r="AV50" t="b">
+        <v>1</v>
+      </c>
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9990,18 +10180,23 @@
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV51" t="inlineStr">
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/805119819_18474649414115878_3601475395675608769_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4MzkwNzYyMjE5MTQ1NDgzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uFX7iLcALa0Q7kNvwHw2pQJ&amp;_nc_oc=Adr1AM4W6nrBHqEDZb1Rd6CHXoaas8AK_K0djVIppxcS5voe1EWQwNV0EvHKVnIMWHM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=ys-wVeJeKGVma3L5g6syHw&amp;_nc_ss=7a22e&amp;oh=00_AQKA7e0JSt9kySIYhyPAQDeSA7VSVTcWNiZ4ZbnfFlFZhw&amp;oe=6AAD12BB</t>
+        </is>
+      </c>
+      <c r="AV51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW51" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/72270-quarteto-marimbondo-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AW51" t="n">
+      <c r="AX51" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX51" t="inlineStr">
+      <c r="AY51" t="inlineStr">
         <is>
           <t>A evidência mais direta indica que o evento Vinilaria Bugio ocorre no Largo da Antonieta em frente ao Bugio Centro, e a página do evento lista o endereço do Bugio Centro como Rua Victor Meirelles, 112, Centro, Florianópolis. Há também fontes complementares confirmando o Largo da Antonieta como área em frente ao Bar Bugio.</t>
         </is>
@@ -10190,18 +10385,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV52" t="inlineStr">
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>https://instagram.flmm1-1.fna.fbcdn.net/v/t51.82787-15/803226600_18018947810923638_5958580088306482895_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4MzgwMzcyNDI1NzgyMzU5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nesO9Cy_aowQ7kNvwEjSQ31&amp;_nc_oc=AdqXo68un7FP2QS4Th11lNbm2FeJeLyE9Q6LRHHEqdOilb5RVjUyC-XVDDars5KbCnQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.flmm1-1.fna&amp;_nc_gid=sfr3tEf0weMd-z2wkJTO_g&amp;_nc_ss=7a22e&amp;oh=00_AQJxOb89_hrGxKO_QQ0bNwFrY90Qgl1dhrUXFt8Mo0kSUQ&amp;oe=6AACFD56</t>
+        </is>
+      </c>
+      <c r="AV52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW52" t="inlineStr">
         <is>
           <t>https://dceven.ufsc.br/localizacao/</t>
         </is>
       </c>
-      <c r="AW52" t="n">
+      <c r="AX52" t="n">
         <v>0.87</v>
       </c>
-      <c r="AX52" t="inlineStr">
+      <c r="AY52" t="inlineStr">
         <is>
           <t>A fonte oficial da UFSC indica a localização do campus Florianópolis como Trindade. Como o evento foi descrito apenas como ocorrendo nos arredores da UFSC, a identificação mais provável é o campus principal da UFSC em Trindade. Não encontrei evidência confiável para um endereço mais específico dentro dos arredores do campus.</t>
         </is>
@@ -10376,12 +10576,17 @@
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>https://scontent-fco2-1.cdninstagram.com/v/t51.82787-15/805485686_18474530350115878_2812815334049977680_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4MzQ1ODM4ODg5NDkyMzgzOTE4NDc0NTMwMzQ3MTE1ODc4.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=6zRDSduCeJkQ7kNvwH6kKLr&amp;_nc_oc=AdpLYutWE2wJPfMDCJcrGZ96kcgmEAIlTbm2p07juCyIbOacVYcVcm_QXXW1kEInusI&amp;_nc_zt=23&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_gid=Uyqi7Mnt4fSD0o5N5NeVHQ&amp;_nc_ss=73a8c&amp;oh=00_AQJl-nbVAGQupnwT0rI71an05NxCLdtRzb0YfzKFf9E3Xg&amp;oe=6AAD10DC</t>
+        </is>
+      </c>
+      <c r="AV53" t="b">
+        <v>1</v>
+      </c>
       <c r="AW53" t="inlineStr"/>
       <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10556,12 +10761,17 @@
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
-      <c r="AU54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>https://instagram.fbcn9-1.fna.fbcdn.net/v/t51.82787-15/802641477_18474508675115878_1643112618131409404_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4MzM0NTI0MzUwMzc1MTIxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XX-VW6yJb9oQ7kNvwE-RDKn&amp;_nc_oc=Adr5xQGR04t1mOWx6Q8y2P78BR8zkxpnPAunGz3j3j7ZAA-h0Z3ya2iuvbMtm7miZqI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbcn9-1.fna&amp;_nc_gid=SuZBE-1b47A7ggbMry_AAw&amp;_nc_ss=7a22e&amp;oh=00_AQK3sz9AkWCn6iS5Ku02Pt-VP3egiaBgbaH4100YewTxDg&amp;oe=6AAD03FB</t>
+        </is>
+      </c>
+      <c r="AV54" t="b">
+        <v>1</v>
+      </c>
       <c r="AW54" t="inlineStr"/>
       <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10740,18 +10950,23 @@
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
-      <c r="AU55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV55" t="inlineStr">
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/802459069_18474441043115878_7144764783054644481_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4MzE3MTQ4Njg2NzI5NDY1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=abM4ARstIicQ7kNvwFLAwbS&amp;_nc_oc=AdpqA57oVb36Y14lVzB5ckJG6PjzlO34zzazMsdig8CqeExglxmA4fm61JfTiRzsf_M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=7sFBb45ULfnAOk9m_yhRbw&amp;_nc_ss=7a22e&amp;oh=00_AQKUv3xCrPWkciLb0UJzcDU9OFvj52vNE-1mho9UTxDSdA&amp;oe=6AACEAA9</t>
+        </is>
+      </c>
+      <c r="AV55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW55" t="inlineStr">
         <is>
           <t>https://troop.is/events/naddr1qvzqqqrukvpzp08t5xjg49jvqg77q54d5smmjastaq8d85zzuwtzdzr0m6fd0z0xqqsrsdn9xv6xxvpcxv6rwcm9vvmxzwf4xanxzc3hxpjkywrpxcurqeshrhdsl</t>
         </is>
       </c>
-      <c r="AW55" t="n">
+      <c r="AX55" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX55" t="inlineStr">
+      <c r="AY55" t="inlineStr">
         <is>
           <t>A fonte consultada associa o evento 'Vinilaria Bugio' ao 'Largo da Antonieta' dentro da Bugio Centro e informa a localização da casa como 'Bugio Centro, R. Victor Meirelles, 112'. Outras fontes reforçam que o Largo da Antonieta fica na Rua Victor Meirelles, no Centro de Florianópolis. Como há evidência convergente, o endereço e bairro mais prováveis são estes.</t>
         </is>
@@ -10934,12 +11149,17 @@
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
-      <c r="AU56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/803067889_18041984531818712_3758717854843473900_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4MzE1MjQ3NDAyOTk4NTQ0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=aAFzW_Q6evQQ7kNvwFEmpBa&amp;_nc_oc=AdpXqNEQ254slefvHejFtMwfpP8lYBmdWYY9lyiQFgzLfYuP4p5bSkj3ewcaKYtcV0E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=k-fIO5AQnJUcZTsTVEz83g&amp;_nc_ss=7a22e&amp;oh=00_AQLEZVtnsaUccWBcdoAKX449ZL2SEfjs6zciNe4SfGOTzg&amp;oe=6AAD07A0</t>
+        </is>
+      </c>
+      <c r="AV56" t="b">
+        <v>1</v>
+      </c>
       <c r="AW56" t="inlineStr"/>
       <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -11118,12 +11338,17 @@
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
-      <c r="AU57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>https://instagram.fpbc4-1.fna.fbcdn.net/v/t51.82787-15/802652719_18018833309923638_2957860155106035555_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4MzE1MzA3MjE0NjMxODYwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FrHSwk2yigQQ7kNvwFjTrpf&amp;_nc_oc=AdqkUsTExZtyOyOXhr1IQoKVQWpuSDFteST48U2ExjHBUbQsna9pwd4YuKWwBcDxvbGFQf1bC-4RuPiB24nt4AMC&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fpbc4-1.fna&amp;_nc_gid=0dDFpzMNPbGVfJvXnk_htA&amp;_nc_ss=7a22e&amp;oh=00_AQI-BvhdVnp3PjfrU1nppm2HakFATS8LyWTVopTb4sGCVA&amp;oe=6AAD0CF3</t>
+        </is>
+      </c>
+      <c r="AV57" t="b">
+        <v>1</v>
+      </c>
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11232,12 +11457,17 @@
           <t>Local não encontrado na HERE nem na pesquisa web</t>
         </is>
       </c>
-      <c r="AU58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/802641318_18102734996620922_7745766315438598077_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk4Mjc2MDU1NjQwMDY0NTA1MzE4MTAyNzM0OTkwNjIwOTIy.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjExNzAuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=LQACZKZf2JoQ7kNvwHxR4TR&amp;_nc_oc=AdrFhjla_tq5g6kC7EPGjA3nWhVZMW_5MLKzgp0lR9O4XnF38qnxun9sAYT8GkhsX2Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=upi_m8G-9qQvxEyuU5eueQ&amp;_nc_ss=7a22e&amp;oh=00_AQIDC4D5zbl1PqdObd8GuhNXz3Zgtx6aks12l_WuAYemOw&amp;oe=6AACF864</t>
+        </is>
+      </c>
+      <c r="AV58" t="b">
+        <v>1</v>
+      </c>
       <c r="AW58" t="inlineStr"/>
       <c r="AX58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -11412,12 +11642,17 @@
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
-      <c r="AU59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/802031174_18627351859057916_7007518338177097654_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4MjcxMjcxMjg1NzAzNTg1NDE4NjI3MzUxODUzMDU3OTE2.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=MqQZ_PTYHTwQ7kNvwHYubDS&amp;_nc_oc=AdrUJ96_60JogZKhbBIPv_Q2Sxx71dWOZ7q2aFK6uKzxZ8dVRKZT8wuTpOrbVT41y9g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=xefaFeUUNmyGEAcdRy6uWQ&amp;_nc_ss=7a22e&amp;oh=00_AQIfdQvAJxyU4dDCelSRuG_c9ZSwP2P8VPGD3doJOPoXVw&amp;oe=6AACF885</t>
+        </is>
+      </c>
+      <c r="AV59" t="b">
+        <v>1</v>
+      </c>
       <c r="AW59" t="inlineStr"/>
       <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -11596,12 +11831,17 @@
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
-      <c r="AU60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>https://scontent-sjc6-1.cdninstagram.com/v/t51.82787-15/801284320_17881559808622100_7316420572762634905_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4MjY4NzUxMDM5NTY2NDk2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTEyMi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AfVDs4MtC4AQ7kNvwGpTUDe&amp;_nc_oc=AdrO4I_7rfuFdgzohP9TeDGSH9IBZDMwv9JGoGeeH6O9nVZqZCLe5TuEFiqFxlfXuS1BAKGcQGSoOmAtuNBZnoGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=KQM9VSUKqWkXDWbqRrMZNw&amp;_nc_ss=7a22e&amp;oh=00_AQJtgxxa3Tro2CegEoi-5qultlnO7H34NquVnp9eEqaoTQ&amp;oe=6AACDEDD</t>
+        </is>
+      </c>
+      <c r="AV60" t="b">
+        <v>1</v>
+      </c>
       <c r="AW60" t="inlineStr"/>
       <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -11780,12 +12020,17 @@
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/801882106_18328646302277782_7214201580796467522_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4MjYzOTYwODM0ODU2MzI5NTE4MzI4NjQ2Mjk2Mjc3Nzgy.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjExNzAuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=UdYWtR_r5VAQ7kNvwE--OTX&amp;_nc_oc=AdrwAfCj7EgU6UFMc5hniSTtQGb0Ma8VbZewBoCIfoyHJQv16_qdGHr90hnHpgWFRgApo5wyZgmxovRcoFlSm0LX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=nk-JqYcn3CoIEx8oau6okw&amp;_nc_ss=7a22e&amp;oh=00_AQJid3ybLpgdMDv8T8ld-7luVK4mLRKKdN-sWjPH_7XQNw&amp;oe=6AACFD1F</t>
+        </is>
+      </c>
+      <c r="AV61" t="b">
+        <v>1</v>
+      </c>
       <c r="AW61" t="inlineStr"/>
       <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -11964,12 +12209,17 @@
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
-      <c r="AU62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/801882106_18328646302277782_7214201580796467522_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4MjYzOTYwODM0ODU2MzI5NTE4MzI4NjQ2Mjk2Mjc3Nzgy.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjExNzAuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=UdYWtR_r5VAQ7kNvwE--OTX&amp;_nc_oc=AdrwAfCj7EgU6UFMc5hniSTtQGb0Ma8VbZewBoCIfoyHJQv16_qdGHr90hnHpgWFRgApo5wyZgmxovRcoFlSm0LX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=nk-JqYcn3CoIEx8oau6okw&amp;_nc_ss=7a22e&amp;oh=00_AQJid3ybLpgdMDv8T8ld-7luVK4mLRKKdN-sWjPH_7XQNw&amp;oe=6AACFD1F</t>
+        </is>
+      </c>
+      <c r="AV62" t="b">
+        <v>1</v>
+      </c>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12154,18 +12404,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV63" t="inlineStr">
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/802223783_18474312904115878_4016662029090323658_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MjYyMzE3NzEzNzMxMTE2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r7uuqbe9O2EQ7kNvwFfmNFC&amp;_nc_oc=AdoxPBJhkrbD0ah_xVPOv29we9yucjnnm8XM14BSXNJnJ4ioZ8p5kg1P1XY4QNoj8ss&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=IZF_5_dZNCkCD7BoBx-hxg&amp;_nc_ss=7a22e&amp;oh=00_AQLY8QVKYtuEbp5bUiPyo_VgNBnxB4st1rwOX29BGCCXkQ&amp;oe=6AACEF5E</t>
+        </is>
+      </c>
+      <c r="AV63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW63" t="inlineStr">
         <is>
           <t>https://www.querole.net/events/3536</t>
         </is>
       </c>
-      <c r="AW63" t="n">
+      <c r="AX63" t="n">
         <v>0.95</v>
       </c>
-      <c r="AX63" t="inlineStr">
+      <c r="AY63" t="inlineStr">
         <is>
           <t>As fontes consultadas associam o Largo da Antonieta ao Bugio Centro e informam o endereço na Rua Victor Meirelles, 112, Centro, Florianópolis - SC. A evidência é consistente entre múltiplas páginas de eventos e referências ao local.</t>
         </is>
@@ -12344,12 +12599,17 @@
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
-      <c r="AU64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>https://instagram.fcpq7-1.fna.fbcdn.net/v/t51.82787-15/801755688_18018748721923638_118781052017302733_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4MjYxNzU3NjM1NDAyNzE4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uCeT_dgk11UQ7kNvwHpSnTB&amp;_nc_oc=AdrHjsuMRUwcz3T0QdDUTQ5QZea4l29f_MPV0Gx1rWLgIPdYp0sQJV2vKA3GZ8zHpDw&amp;_nc_ad=z-m&amp;_nc_cid=1138&amp;_nc_zt=23&amp;_nc_ht=instagram.fcpq7-1.fna&amp;_nc_gid=wKeoR1Pr6Y3ThqFy0-oGTA&amp;_nc_ss=7a22e&amp;oh=00_AQI1vf1aW0gzyCspaxoYcvbRKlQfxMCHeLmo-GEk9b78DQ&amp;oe=6AAD0684</t>
+        </is>
+      </c>
+      <c r="AV64" t="b">
+        <v>1</v>
+      </c>
       <c r="AW64" t="inlineStr"/>
       <c r="AX64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -12540,12 +12800,17 @@
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
-      <c r="AU65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>https://instagram.fvce1-1.fna.fbcdn.net/v/t51.82787-15/801582930_18328616830277782_8658820114883937248_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4MjQ5MjA1NTA5NDU5MzYzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=D2_W2Volj4QQ7kNvwEGezXN&amp;_nc_oc=AdrbXiIGG70MuxfV5U2-3jC7IMsxvjyZP0_8Jsch8j2aJif08JFddgmsFNQ38sQ4_mQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fvce1-1.fna&amp;_nc_gid=A9FFoTimxcFknnwmoVspMA&amp;_nc_ss=7a22e&amp;oh=00_AQJ0ZRF2ZInoQBTvCtucGVdlOIDfPD-uZ-hTR11gjMXOiA&amp;oe=6AAD1698</t>
+        </is>
+      </c>
+      <c r="AV65" t="b">
+        <v>1</v>
+      </c>
       <c r="AW65" t="inlineStr"/>
       <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12720,18 +12985,23 @@
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
-      <c r="AU66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV66" t="inlineStr">
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-2.cdninstagram.com/v/t51.82787-15/801457050_18474259702115878_3873155466998823716_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MjQ1Njk0NjI0NDcwOTM4NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FKpJobpcP-cQ7kNvwE7H5yk&amp;_nc_oc=AdrSdw3lLOHcRZ9Th7upnP3phNJ-Z9OVThDqj4hVnBSk2jypRTiIEzxDYkMDuXDlCis&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-2.cdninstagram.com&amp;_nc_gid=rq5RrIZTNyQYCaOQM06m-g&amp;_nc_ss=7a22e&amp;oh=00_AQK7ouDvf0vR05g3UDw9Scr297Gj9TakRcdIyAdOacp-vA&amp;oe=6AAD01D5</t>
+        </is>
+      </c>
+      <c r="AV66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW66" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com.br/Restaurant_Review-g303576-d33047585-Reviews-Bugio_Centro-Florianopolis_State_of_Santa_Catarina.html</t>
         </is>
       </c>
-      <c r="AW66" t="n">
+      <c r="AX66" t="n">
         <v>0.91</v>
       </c>
-      <c r="AX66" t="inlineStr">
+      <c r="AY66" t="inlineStr">
         <is>
           <t>A busca relaciona diretamente o evento 'Samba da Antonieta' ao Bugio Centro em Florianópolis, e a página consultada informa o endereço Rua Victor Meirelles, 112. Outras fontes também associam o Samba da Antonieta ao Bugio Centro/Largo da Antonieta, reforçando a identificação do espaço no Centro de Florianópolis.</t>
         </is>
@@ -12910,12 +13180,17 @@
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
-      <c r="AU67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV67" t="inlineStr"/>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/801219947_18474156025115878_8124390036068708275_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4MjAwMzE5NDM1NTM4OTY0MjE4NDc0MTU2MDE5MTE1ODc4.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=12MSTtQLlJkQ7kNvwHo6QqK&amp;_nc_oc=AdrGDQo12u9N63JoqLwgVVTgEnbVGuD_AbQZDXAOiSPbm_kZomBgBPcmhKOCV7cJ4UU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=xamxsirQ-qeJld8uX4j8Mg&amp;_nc_ss=7a22e&amp;oh=00_AQJSUbG9Mu8dApiiG897_j4BdPzy3CdGWTgr895ZdExDVw&amp;oe=6AACF999</t>
+        </is>
+      </c>
+      <c r="AV67" t="b">
+        <v>1</v>
+      </c>
       <c r="AW67" t="inlineStr"/>
       <c r="AX67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13102,12 +13377,17 @@
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
-      <c r="AU68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/801219931_18018623468923638_5540943341840814421_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4MTk5MjAwMDcxNzE5OTEwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PqrckO9TPkIQ7kNvwHPBBYR&amp;_nc_oc=AdqFX-NfQzRckYeGIm4HIwyXMxEAXm1nV6u95OZWxdOdkC4FIa-sMsfk8wOBMGuZKaWRmxjXAXdQu2VwRdM5uMLG&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=rDPtVHPgRtQ84AG5wwEszw&amp;_nc_ss=7a22e&amp;oh=00_AQLOJWZc5afw25WnwpGj3mrY9ptUJTDOV6I2MNHxJWVmoQ&amp;oe=6AAD04B7</t>
+        </is>
+      </c>
+      <c r="AV68" t="b">
+        <v>1</v>
+      </c>
       <c r="AW68" t="inlineStr"/>
       <c r="AX68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13290,12 +13570,17 @@
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
-      <c r="AU69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>https://instagram.fmlm4-1.fna.fbcdn.net/v/t51.82787-15/800514417_18474137782115878_1576852022239977308_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MTkxNDIyNTMwMTk2NDQwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XURNHuiUtR0Q7kNvwH9dSSc&amp;_nc_oc=Adp9A3yz9G0xmfVb8_QH3rLnw1avCtAyQeQpdA8KQ8vGiOFWfJ9W_0gEPWjug6tYHFg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmlm4-1.fna&amp;_nc_gid=TcHc6AHk1cR6e3NX0D3XaA&amp;_nc_ss=7a22e&amp;oh=00_AQJoVtXBESbLFgaYG7VBUPC0wQTILV0xFBnMoS4_6KXMiA&amp;oe=6AACE4FA</t>
+        </is>
+      </c>
+      <c r="AV69" t="b">
+        <v>1</v>
+      </c>
       <c r="AW69" t="inlineStr"/>
       <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13478,12 +13763,17 @@
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
-      <c r="AU70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>https://instagram.fmlm4-1.fna.fbcdn.net/v/t51.82787-15/800514417_18474137782115878_1576852022239977308_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MTkxNDIyNTMwMTk2NDQwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XURNHuiUtR0Q7kNvwH9dSSc&amp;_nc_oc=Adp9A3yz9G0xmfVb8_QH3rLnw1avCtAyQeQpdA8KQ8vGiOFWfJ9W_0gEPWjug6tYHFg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmlm4-1.fna&amp;_nc_gid=TcHc6AHk1cR6e3NX0D3XaA&amp;_nc_ss=7a22e&amp;oh=00_AQJoVtXBESbLFgaYG7VBUPC0wQTILV0xFBnMoS4_6KXMiA&amp;oe=6AACE4FA</t>
+        </is>
+      </c>
+      <c r="AV70" t="b">
+        <v>1</v>
+      </c>
       <c r="AW70" t="inlineStr"/>
       <c r="AX70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13658,12 +13948,17 @@
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
-      <c r="AU71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>https://instagram.fmlm4-1.fna.fbcdn.net/v/t51.82787-15/800514417_18474137782115878_1576852022239977308_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MTkxNDIyNTMwMTk2NDQwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XURNHuiUtR0Q7kNvwH9dSSc&amp;_nc_oc=Adp9A3yz9G0xmfVb8_QH3rLnw1avCtAyQeQpdA8KQ8vGiOFWfJ9W_0gEPWjug6tYHFg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmlm4-1.fna&amp;_nc_gid=TcHc6AHk1cR6e3NX0D3XaA&amp;_nc_ss=7a22e&amp;oh=00_AQJoVtXBESbLFgaYG7VBUPC0wQTILV0xFBnMoS4_6KXMiA&amp;oe=6AACE4FA</t>
+        </is>
+      </c>
+      <c r="AV71" t="b">
+        <v>1</v>
+      </c>
       <c r="AW71" t="inlineStr"/>
       <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13842,12 +14137,17 @@
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
-      <c r="AU72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>https://instagram.fmlm4-1.fna.fbcdn.net/v/t51.82787-15/800514417_18474137782115878_1576852022239977308_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MTkxNDIyNTMwMTk2NDQwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XURNHuiUtR0Q7kNvwH9dSSc&amp;_nc_oc=Adp9A3yz9G0xmfVb8_QH3rLnw1avCtAyQeQpdA8KQ8vGiOFWfJ9W_0gEPWjug6tYHFg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmlm4-1.fna&amp;_nc_gid=TcHc6AHk1cR6e3NX0D3XaA&amp;_nc_ss=7a22e&amp;oh=00_AQJoVtXBESbLFgaYG7VBUPC0wQTILV0xFBnMoS4_6KXMiA&amp;oe=6AACE4FA</t>
+        </is>
+      </c>
+      <c r="AV72" t="b">
+        <v>1</v>
+      </c>
       <c r="AW72" t="inlineStr"/>
       <c r="AX72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -14030,12 +14330,17 @@
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
-      <c r="AU73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>https://instagram.fmlm4-1.fna.fbcdn.net/v/t51.82787-15/800514417_18474137782115878_1576852022239977308_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MTkxNDIyNTMwMTk2NDQwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XURNHuiUtR0Q7kNvwH9dSSc&amp;_nc_oc=Adp9A3yz9G0xmfVb8_QH3rLnw1avCtAyQeQpdA8KQ8vGiOFWfJ9W_0gEPWjug6tYHFg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmlm4-1.fna&amp;_nc_gid=TcHc6AHk1cR6e3NX0D3XaA&amp;_nc_ss=7a22e&amp;oh=00_AQJoVtXBESbLFgaYG7VBUPC0wQTILV0xFBnMoS4_6KXMiA&amp;oe=6AACE4FA</t>
+        </is>
+      </c>
+      <c r="AV73" t="b">
+        <v>1</v>
+      </c>
       <c r="AW73" t="inlineStr"/>
       <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -14218,12 +14523,17 @@
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
-      <c r="AU74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV74" t="inlineStr"/>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>https://instagram.fmlm4-1.fna.fbcdn.net/v/t51.82787-15/800514417_18474137782115878_1576852022239977308_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MTkxNDIyNTMwMTk2NDQwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XURNHuiUtR0Q7kNvwH9dSSc&amp;_nc_oc=Adp9A3yz9G0xmfVb8_QH3rLnw1avCtAyQeQpdA8KQ8vGiOFWfJ9W_0gEPWjug6tYHFg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmlm4-1.fna&amp;_nc_gid=TcHc6AHk1cR6e3NX0D3XaA&amp;_nc_ss=7a22e&amp;oh=00_AQJoVtXBESbLFgaYG7VBUPC0wQTILV0xFBnMoS4_6KXMiA&amp;oe=6AACE4FA</t>
+        </is>
+      </c>
+      <c r="AV74" t="b">
+        <v>1</v>
+      </c>
       <c r="AW74" t="inlineStr"/>
       <c r="AX74" t="inlineStr"/>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -14398,12 +14708,17 @@
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
-      <c r="AU75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV75" t="inlineStr"/>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>https://instagram.fmlm4-1.fna.fbcdn.net/v/t51.82787-15/800514417_18474137782115878_1576852022239977308_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MTkxNDIyNTMwMTk2NDQwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XURNHuiUtR0Q7kNvwH9dSSc&amp;_nc_oc=Adp9A3yz9G0xmfVb8_QH3rLnw1avCtAyQeQpdA8KQ8vGiOFWfJ9W_0gEPWjug6tYHFg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmlm4-1.fna&amp;_nc_gid=TcHc6AHk1cR6e3NX0D3XaA&amp;_nc_ss=7a22e&amp;oh=00_AQJoVtXBESbLFgaYG7VBUPC0wQTILV0xFBnMoS4_6KXMiA&amp;oe=6AACE4FA</t>
+        </is>
+      </c>
+      <c r="AV75" t="b">
+        <v>1</v>
+      </c>
       <c r="AW75" t="inlineStr"/>
       <c r="AX75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14578,12 +14893,17 @@
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
-      <c r="AU76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV76" t="inlineStr"/>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>https://instagram.fmlm4-1.fna.fbcdn.net/v/t51.82787-15/800514417_18474137782115878_1576852022239977308_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MTkxNDIyNTMwMTk2NDQwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XURNHuiUtR0Q7kNvwH9dSSc&amp;_nc_oc=Adp9A3yz9G0xmfVb8_QH3rLnw1avCtAyQeQpdA8KQ8vGiOFWfJ9W_0gEPWjug6tYHFg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmlm4-1.fna&amp;_nc_gid=TcHc6AHk1cR6e3NX0D3XaA&amp;_nc_ss=7a22e&amp;oh=00_AQJoVtXBESbLFgaYG7VBUPC0wQTILV0xFBnMoS4_6KXMiA&amp;oe=6AACE4FA</t>
+        </is>
+      </c>
+      <c r="AV76" t="b">
+        <v>1</v>
+      </c>
       <c r="AW76" t="inlineStr"/>
       <c r="AX76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -14762,18 +15082,23 @@
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
-      <c r="AU77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV77" t="inlineStr">
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>https://scontent-nrt1-2.cdninstagram.com/v/t51.82787-15/800950239_18018611381923638_4483615283596600036_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4MTg5OTQ1MDgxNjI0NjU0MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=IUtei-g5trEQ7kNvwHxnjaA&amp;_nc_oc=Adr7CAk6vdT6XV-ywEaH45bGPZl8kExnFk684hMnCTkX3pBV1dI_oYS8H6CjdA-DG8Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=AgfnSloADnS8FNbpvNoi0g&amp;_nc_ss=7a22e&amp;oh=00_AQI3P0fITBVSWoorTDCmoeThCgtkgT9NJt_RFbD_Q48YxA&amp;oe=6AACE5EA</t>
+        </is>
+      </c>
+      <c r="AV77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW77" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/76706-rafa-puerta-bugio-trindade-florianopolis</t>
         </is>
       </c>
-      <c r="AW77" t="n">
+      <c r="AX77" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX77" t="inlineStr">
+      <c r="AY77" t="inlineStr">
         <is>
           <t>A agenda do evento informa explicitamente que a apresentação ocorreu no Bugio Trindade e exibe o endereço Servidão Cristiano Vanderlei Faria, 25, Trindade, Florianópolis - SC. A mesma identificação aparece em outras fontes consultadas, reforçando a evidência.</t>
         </is>
@@ -14960,12 +15285,17 @@
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
-      <c r="AU78" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV78" t="inlineStr"/>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>https://scontent-gru1-2.cdninstagram.com/v/t51.82787-15/801354887_18041748440818712_3726810039286798254_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTgyNjE3NjQ3NzA1MzM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=hpnOv3svtaEQ7kNvwEZvbhK&amp;_nc_oc=AdrZ-0Porqgy7stXqqaS63muWqoQkFvU0fm52qRSmo_d0xsGB3E0ItkCloNZzanwFIg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=MtrclPEX5MjwbyA1-kadsA&amp;_nc_ss=7a22e&amp;oh=00_AQJYCwUHmSQU27ZHWvCKjrbZ_DOwe4VTKPOVGPg7ulDT_g&amp;oe=6AACEA7C</t>
+        </is>
+      </c>
+      <c r="AV78" t="b">
+        <v>1</v>
+      </c>
       <c r="AW78" t="inlineStr"/>
       <c r="AX78" t="inlineStr"/>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -15140,18 +15470,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV79" t="inlineStr">
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>https://scontent-gru1-2.cdninstagram.com/v/t51.82787-15/801354887_18041748440818712_3726810039286798254_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTgyNjE3NjQ3NzA1MzM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=hpnOv3svtaEQ7kNvwEZvbhK&amp;_nc_oc=AdrZ-0Porqgy7stXqqaS63muWqoQkFvU0fm52qRSmo_d0xsGB3E0ItkCloNZzanwFIg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=MtrclPEX5MjwbyA1-kadsA&amp;_nc_ss=7a22e&amp;oh=00_AQJYCwUHmSQU27ZHWvCKjrbZ_DOwe4VTKPOVGPg7ulDT_g&amp;oe=6AACEA7C</t>
+        </is>
+      </c>
+      <c r="AV79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW79" t="inlineStr">
         <is>
           <t>https://museudasilusoes.com.br/</t>
         </is>
       </c>
-      <c r="AW79" t="n">
+      <c r="AX79" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX79" t="inlineStr">
+      <c r="AY79" t="inlineStr">
         <is>
           <t>A página oficial do Museu das Ilusões informa explicitamente a unidade em Florianópolis no Floripa Shopping, com endereço SC-401, 3116 – Saco Grande, Florianópolis – SC, e menciona o piso L3. Isso confirma o estabelecimento, o endereço e o bairro com alta confiabilidade.</t>
         </is>
@@ -15340,18 +15675,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV80" t="inlineStr">
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>https://scontent-gru1-2.cdninstagram.com/v/t51.82787-15/801354887_18041748440818712_3726810039286798254_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTgyNjE3NjQ3NzA1MzM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=hpnOv3svtaEQ7kNvwEZvbhK&amp;_nc_oc=AdrZ-0Porqgy7stXqqaS63muWqoQkFvU0fm52qRSmo_d0xsGB3E0ItkCloNZzanwFIg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=MtrclPEX5MjwbyA1-kadsA&amp;_nc_ss=7a22e&amp;oh=00_AQJYCwUHmSQU27ZHWvCKjrbZ_DOwe4VTKPOVGPg7ulDT_g&amp;oe=6AACEA7C</t>
+        </is>
+      </c>
+      <c r="AV80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW80" t="inlineStr">
         <is>
           <t>https://www.alesc.sc.gov.br/imprensa/noticia/exposicao-desdobramentos-da-transmutacao-explora-processo-de-ressignificar-vivencias/</t>
         </is>
       </c>
-      <c r="AW80" t="n">
+      <c r="AX80" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX80" t="inlineStr">
+      <c r="AY80" t="inlineStr">
         <is>
           <t>A fonte oficial da Alesc informa que a exposição ocorre na Galeria de Arte Ernesto Meyer Filho, no saguão do Palácio Barriga Verde, com endereço na Rua Dr. Jorge Luz Fontes, 310, Florianópolis. Outra página institucional da própria Alesc confirma que a galeria fica no hall do Palácio Barriga Verde, no Centro.</t>
         </is>
@@ -15524,18 +15864,23 @@
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
-      <c r="AU81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV81" t="inlineStr">
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>https://scontent-gru1-2.cdninstagram.com/v/t51.82787-15/801354887_18041748440818712_3726810039286798254_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTgyNjE3NjQ3NzA1MzM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=hpnOv3svtaEQ7kNvwEZvbhK&amp;_nc_oc=AdrZ-0Porqgy7stXqqaS63muWqoQkFvU0fm52qRSmo_d0xsGB3E0ItkCloNZzanwFIg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=MtrclPEX5MjwbyA1-kadsA&amp;_nc_ss=7a22e&amp;oh=00_AQJYCwUHmSQU27ZHWvCKjrbZ_DOwe4VTKPOVGPg7ulDT_g&amp;oe=6AACEA7C</t>
+        </is>
+      </c>
+      <c r="AV81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW81" t="inlineStr">
         <is>
           <t>https://www.floripashopping.com.br/</t>
         </is>
       </c>
-      <c r="AW81" t="n">
+      <c r="AX81" t="n">
         <v>0.96</v>
       </c>
-      <c r="AX81" t="inlineStr">
+      <c r="AY81" t="inlineStr">
         <is>
           <t>Há evidência direta de que o Festival de Circo ocorre no Floripa Shopping e que o shopping informa seu endereço em Saco Grande. Também há material do próprio shopping indicando eventos sazonais no vão central; por isso, o espaço provável é o Floripa Shopping, na área do vão central/praça de eventos.</t>
         </is>
@@ -15714,18 +16059,23 @@
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
-      <c r="AU82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV82" t="inlineStr">
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>https://scontent-gru1-2.cdninstagram.com/v/t51.82787-15/801354887_18041748440818712_3726810039286798254_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTgyNjE3NjQ3NzA1MzM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=hpnOv3svtaEQ7kNvwEZvbhK&amp;_nc_oc=AdrZ-0Porqgy7stXqqaS63muWqoQkFvU0fm52qRSmo_d0xsGB3E0ItkCloNZzanwFIg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=MtrclPEX5MjwbyA1-kadsA&amp;_nc_ss=7a22e&amp;oh=00_AQJYCwUHmSQU27ZHWvCKjrbZ_DOwe4VTKPOVGPg7ulDT_g&amp;oe=6AACEA7C</t>
+        </is>
+      </c>
+      <c r="AV82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW82" t="inlineStr">
         <is>
           <t>https://www.arenaopus.com/</t>
         </is>
       </c>
-      <c r="AW82" t="n">
+      <c r="AX82" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX82" t="inlineStr">
+      <c r="AY82" t="inlineStr">
         <is>
           <t>A fonte oficial da Arena Opus informa o endereço na SC-281, 4000, em Sertão do Maruim, São José/SC. Como o local informado no evento é Arena Opus, a identificação do estabelecimento é confiável.</t>
         </is>
@@ -15904,18 +16254,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV83" t="inlineStr">
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>https://scontent-gru1-2.cdninstagram.com/v/t51.82787-15/801354887_18041748440818712_3726810039286798254_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTgyNjE3NjQ3NzA1MzM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=hpnOv3svtaEQ7kNvwEZvbhK&amp;_nc_oc=AdrZ-0Porqgy7stXqqaS63muWqoQkFvU0fm52qRSmo_d0xsGB3E0ItkCloNZzanwFIg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=MtrclPEX5MjwbyA1-kadsA&amp;_nc_ss=7a22e&amp;oh=00_AQJYCwUHmSQU27ZHWvCKjrbZ_DOwe4VTKPOVGPg7ulDT_g&amp;oe=6AACEA7C</t>
+        </is>
+      </c>
+      <c r="AV83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW83" t="inlineStr">
         <is>
           <t>https://www.santacatarinadanca.com.br/</t>
         </is>
       </c>
-      <c r="AW83" t="n">
+      <c r="AX83" t="n">
         <v>0.88</v>
       </c>
-      <c r="AX83" t="inlineStr">
+      <c r="AY83" t="inlineStr">
         <is>
           <t>O evento consultado aparece com realização no Teatro Ademir Rosa, no CIC, em Florianópolis. Para o CIC/Teatro Ademir Rosa, a fonte web encontrada indica o complexo na Av. Gov. Irineu Bornhausen, 5600, no bairro Agronômica. Por isso, o nome provável do espaço é Teatro Ademir Rosa (CIC).</t>
         </is>
@@ -16096,18 +16451,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV84" t="inlineStr">
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>https://scontent-gru1-2.cdninstagram.com/v/t51.82787-15/801354887_18041748440818712_3726810039286798254_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTgyNjE3NjQ3NzA1MzM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=hpnOv3svtaEQ7kNvwEZvbhK&amp;_nc_oc=AdrZ-0Porqgy7stXqqaS63muWqoQkFvU0fm52qRSmo_d0xsGB3E0ItkCloNZzanwFIg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=MtrclPEX5MjwbyA1-kadsA&amp;_nc_ss=7a22e&amp;oh=00_AQJYCwUHmSQU27ZHWvCKjrbZ_DOwe4VTKPOVGPg7ulDT_g&amp;oe=6AACEA7C</t>
+        </is>
+      </c>
+      <c r="AV84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW84" t="inlineStr">
         <is>
           <t>https://www.cultura.sc.gov.br/programacao/2102-cineclube-escolar-da-mostra-de-cinema-infantil-de-florianopolis</t>
         </is>
       </c>
-      <c r="AW84" t="n">
+      <c r="AX84" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX84" t="inlineStr">
+      <c r="AY84" t="inlineStr">
         <is>
           <t>A fonte consultada informa que o Cineclube da Mostra de Cinema Infantil ocorre no Cinema Gilberto Gerlach, no Centro Integrado de Cultura (CIC), com endereço em Av. Gov. Irineu Bornhausen, 5600, bairro Agronômica, Florianópolis - SC.</t>
         </is>
@@ -16290,12 +16650,17 @@
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
-      <c r="AU85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV85" t="inlineStr"/>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>https://scontent-gru1-2.cdninstagram.com/v/t51.82787-15/801354887_18041748440818712_3726810039286798254_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTgyNjE3NjQ3NzA1MzM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=hpnOv3svtaEQ7kNvwEZvbhK&amp;_nc_oc=AdrZ-0Porqgy7stXqqaS63muWqoQkFvU0fm52qRSmo_d0xsGB3E0ItkCloNZzanwFIg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=MtrclPEX5MjwbyA1-kadsA&amp;_nc_ss=7a22e&amp;oh=00_AQJYCwUHmSQU27ZHWvCKjrbZ_DOwe4VTKPOVGPg7ulDT_g&amp;oe=6AACEA7C</t>
+        </is>
+      </c>
+      <c r="AV85" t="b">
+        <v>1</v>
+      </c>
       <c r="AW85" t="inlineStr"/>
       <c r="AX85" t="inlineStr"/>
+      <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16480,18 +16845,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV86" t="inlineStr">
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>https://scontent-gru1-2.cdninstagram.com/v/t51.82787-15/801354887_18041748440818712_3726810039286798254_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTgyNjE3NjQ3NzA1MzM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuOTYwLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=hpnOv3svtaEQ7kNvwEZvbhK&amp;_nc_oc=AdrZ-0Porqgy7stXqqaS63muWqoQkFvU0fm52qRSmo_d0xsGB3E0ItkCloNZzanwFIg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=MtrclPEX5MjwbyA1-kadsA&amp;_nc_ss=7a22e&amp;oh=00_AQJYCwUHmSQU27ZHWvCKjrbZ_DOwe4VTKPOVGPg7ulDT_g&amp;oe=6AACEA7C</t>
+        </is>
+      </c>
+      <c r="AV86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW86" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/agenda/restaurantes</t>
         </is>
       </c>
-      <c r="AW86" t="n">
+      <c r="AX86" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX86" t="inlineStr">
+      <c r="AY86" t="inlineStr">
         <is>
           <t>Há evidência consistente de que o evento ocorreu no Centro de Eventos Oceania, também identificado como Oceania Park Hotel Spa &amp; Convention Center by RB Hotelaria, com endereço na R. do Marisco, 550, Ingleses, Florianópolis. A fonte consultada traz explicitamente o local e o endereço.</t>
         </is>
@@ -16682,12 +17052,17 @@
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
-      <c r="AU87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV87" t="inlineStr"/>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>https://instagram.fmex5-1.fna.fbcdn.net/v/t51.82787-15/800945402_18018580427923638_2748016589704986294_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk4MTc1MjI3ODgxMTkzNTM5Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=dfUH-uSZLBMQ7kNvwHYdnOt&amp;_nc_oc=Ado-Y56NxI43K67_5JnzK-iLm8inylQSJuGJoGlRbaCUCRW5A8ye2gZA9V-oaIwHwp9O8FinplukW1zSinalbIfY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmex5-1.fna&amp;_nc_gid=BfUxRzuHeeLU39qJ5Dax4Q&amp;_nc_ss=7a22e&amp;oh=00_AQIXgWkTMB_66TS5xuV1iwX9BArrdD7MNooR2isWNbkgvg&amp;oe=6AAD0137</t>
+        </is>
+      </c>
+      <c r="AV87" t="b">
+        <v>1</v>
+      </c>
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr"/>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -16876,18 +17251,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV88" t="inlineStr">
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>https://instagram.fyzd1-2.fna.fbcdn.net/v/t51.82787-15/800755762_18474084979115878_1312462304385718114_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4MTcyMDE1OTIxNzk3Mjk0Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ORgP0CNc8r4Q7kNvwG5T_9L&amp;_nc_oc=Adrlo2wqtj30iDQoTewfGhMr_gsbWJyOgdQxQVT9J6te1tuI9fot7M_Hkp2N3nFeae4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyzd1-2.fna&amp;_nc_gid=MeJGRBqt5mtf4-y1WWNzqw&amp;_nc_ss=7a22e&amp;oh=00_AQLWZ41VY7Fdh0bN7U62lvi48h3cse0dQ0IrM9zdTkAsFA&amp;oe=6AAD0135</t>
+        </is>
+      </c>
+      <c r="AV88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW88" t="inlineStr">
         <is>
           <t>https://www.correiosc.com.br/projeto-nossa-musica-sc-da-camerata-florianopolis-sera-exibido-ao-ar-livre/</t>
         </is>
       </c>
-      <c r="AW88" t="n">
+      <c r="AX88" t="n">
         <v>0.91</v>
       </c>
-      <c r="AX88" t="inlineStr">
+      <c r="AY88" t="inlineStr">
         <is>
           <t>A evidência mais forte aponta que o evento ocorreu em frente ao Bar Bugio, no Largo da Antonieta, na Rua Victor Meirelles, Centro, Florianópolis. A fonte também identifica o Bugio Centro na Rua Victor Meirelles, 112, o que sustenta o nome provável do espaço.</t>
         </is>
@@ -17076,18 +17456,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV89" t="inlineStr">
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>https://instagram.fsac1-1.fna.fbcdn.net/v/t51.82787-15/794032625_18473990983115878_5396724536678069775_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4MTI5MjEzMzQyMjc4NzkzNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=klIGrfzcO34Q7kNvwFsPEEs&amp;_nc_oc=AdpEXyGW9xye9KQz8l2rHSTt8SZ0bprN21ZoI0tGPjLCKE3SS8EDEVJRsCBqSFCx8Q0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsac1-1.fna&amp;_nc_gid=1OwPePguA2Q2JyYqdf_K9A&amp;_nc_ss=7a22e&amp;oh=00_AQIdejQZvtfxAaN0fJBmiI6tatN-SWpOGyL6rip011-fZw&amp;oe=6AACE5AC</t>
+        </is>
+      </c>
+      <c r="AV89" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW89" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/78237-forro-de-base-delas-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AW89" t="n">
+      <c r="AX89" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX89" t="inlineStr">
+      <c r="AY89" t="inlineStr">
         <is>
           <t>O evento 'Forró de Base Delas' aparece associado ao perfil @bugiocentro e à programação da Bugio Centro, com o local explicitamente indicado como Bugio Centro e menção ao 'Largo da Antonieta' na mesma agenda. A fonte consultada informa o endereço da casa como Rua Victor Meirelles, 112 - Centro, Florianópolis - SC. Como o pedido exige apenas a identificação provável do espaço, o nome mais seguro é Bugio Centro / Largo da Antonieta, no bairro Centro.</t>
         </is>
@@ -17266,12 +17651,17 @@
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
-      <c r="AU90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV90" t="inlineStr"/>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/799634250_18113463689517524_9201125617776093742_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MTIwMTE5ODc4NjM5MzA1OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTE5NS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=epJ09cKUjOoQ7kNvwGVkh8d&amp;_nc_oc=AdpXvGHZuzz46taByumoPwjs3i1g02fIwpMcXR-53hgQczi4Utq6-dYltnmdazGUPx4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=KoaDbpPGNLgvfx2NZ3XUzg&amp;_nc_ss=7a22e&amp;oh=00_AQIYhGbIWvTvAfSjGQ-e1QqgKV-0moi6RnqY9Dp8DU2gqw&amp;oe=6AAD0782</t>
+        </is>
+      </c>
+      <c r="AV90" t="b">
+        <v>1</v>
+      </c>
       <c r="AW90" t="inlineStr"/>
       <c r="AX90" t="inlineStr"/>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -17450,12 +17840,17 @@
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
-      <c r="AU91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV91" t="inlineStr"/>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t51.82787-15/798415149_18018446537923638_7893723677252007549_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTAwOTMzNjA5MDc5NTM3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=WsZMHEVfy7IQ7kNvwFulIFG&amp;_nc_oc=AdoxBzCPnPbhh_dUu42n8H9cl1v2I4wZ0cupukbvLktEJmMcL1dijOEXen0uda7aWU3WuCupVW-kjiGs1lWyRBhY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=YZRog_OLc2kVrTTBcs02lw&amp;_nc_ss=7a22e&amp;oh=00_AQIqGy0Zqp8omgG3ORGnJ-pttP_zSVjYXmhmU2_B8j2gTQ&amp;oe=6AACFA0F</t>
+        </is>
+      </c>
+      <c r="AV91" t="b">
+        <v>1</v>
+      </c>
       <c r="AW91" t="inlineStr"/>
       <c r="AX91" t="inlineStr"/>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17634,12 +18029,17 @@
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
-      <c r="AU92" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV92" t="inlineStr"/>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t51.82787-15/798415149_18018446537923638_7893723677252007549_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTAwOTMzNjA5MDc5NTM3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=WsZMHEVfy7IQ7kNvwFulIFG&amp;_nc_oc=AdoxBzCPnPbhh_dUu42n8H9cl1v2I4wZ0cupukbvLktEJmMcL1dijOEXen0uda7aWU3WuCupVW-kjiGs1lWyRBhY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=YZRog_OLc2kVrTTBcs02lw&amp;_nc_ss=7a22e&amp;oh=00_AQIqGy0Zqp8omgG3ORGnJ-pttP_zSVjYXmhmU2_B8j2gTQ&amp;oe=6AACFA0F</t>
+        </is>
+      </c>
+      <c r="AV92" t="b">
+        <v>1</v>
+      </c>
       <c r="AW92" t="inlineStr"/>
       <c r="AX92" t="inlineStr"/>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17818,12 +18218,17 @@
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
-      <c r="AU93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV93" t="inlineStr"/>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t51.82787-15/798415149_18018446537923638_7893723677252007549_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTAwOTMzNjA5MDc5NTM3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=WsZMHEVfy7IQ7kNvwFulIFG&amp;_nc_oc=AdoxBzCPnPbhh_dUu42n8H9cl1v2I4wZ0cupukbvLktEJmMcL1dijOEXen0uda7aWU3WuCupVW-kjiGs1lWyRBhY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=YZRog_OLc2kVrTTBcs02lw&amp;_nc_ss=7a22e&amp;oh=00_AQIqGy0Zqp8omgG3ORGnJ-pttP_zSVjYXmhmU2_B8j2gTQ&amp;oe=6AACFA0F</t>
+        </is>
+      </c>
+      <c r="AV93" t="b">
+        <v>1</v>
+      </c>
       <c r="AW93" t="inlineStr"/>
       <c r="AX93" t="inlineStr"/>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18002,12 +18407,17 @@
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
-      <c r="AU94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV94" t="inlineStr"/>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t51.82787-15/798415149_18018446537923638_7893723677252007549_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTAwOTMzNjA5MDc5NTM3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=WsZMHEVfy7IQ7kNvwFulIFG&amp;_nc_oc=AdoxBzCPnPbhh_dUu42n8H9cl1v2I4wZ0cupukbvLktEJmMcL1dijOEXen0uda7aWU3WuCupVW-kjiGs1lWyRBhY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=YZRog_OLc2kVrTTBcs02lw&amp;_nc_ss=7a22e&amp;oh=00_AQIqGy0Zqp8omgG3ORGnJ-pttP_zSVjYXmhmU2_B8j2gTQ&amp;oe=6AACFA0F</t>
+        </is>
+      </c>
+      <c r="AV94" t="b">
+        <v>1</v>
+      </c>
       <c r="AW94" t="inlineStr"/>
       <c r="AX94" t="inlineStr"/>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -18186,12 +18596,17 @@
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
-      <c r="AU95" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV95" t="inlineStr"/>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t51.82787-15/798415149_18018446537923638_7893723677252007549_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MTAwOTMzNjA5MDc5NTM3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=WsZMHEVfy7IQ7kNvwFulIFG&amp;_nc_oc=AdoxBzCPnPbhh_dUu42n8H9cl1v2I4wZ0cupukbvLktEJmMcL1dijOEXen0uda7aWU3WuCupVW-kjiGs1lWyRBhY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=YZRog_OLc2kVrTTBcs02lw&amp;_nc_ss=7a22e&amp;oh=00_AQIqGy0Zqp8omgG3ORGnJ-pttP_zSVjYXmhmU2_B8j2gTQ&amp;oe=6AACFA0F</t>
+        </is>
+      </c>
+      <c r="AV95" t="b">
+        <v>1</v>
+      </c>
       <c r="AW95" t="inlineStr"/>
       <c r="AX95" t="inlineStr"/>
+      <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18370,18 +18785,23 @@
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
-      <c r="AU96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV96" t="inlineStr">
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/800258762_18473908174115878_3385843539327881206_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4MDk3NzQxNDgzMDI2OTk1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1XqXjiPRO2oQ7kNvwEO05oc&amp;_nc_oc=AdozXyoSwSQkP3_uEQWfaViDXeLHSXoQWL9JFZqeLPYKEXV3pAF4uq88nrdGMECgiTM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=VYRPdXRz0yW74zIiqXhBSA&amp;_nc_ss=7a22e&amp;oh=00_AQJs_UWMShu36cnR9dWgJnzI5u7ruOMjNE6mnCVdh6uc7g&amp;oe=6AAD12A0</t>
+        </is>
+      </c>
+      <c r="AV96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW96" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/72270-quarteto-marimbondo-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AW96" t="n">
+      <c r="AX96" t="n">
         <v>0.96</v>
       </c>
-      <c r="AX96" t="inlineStr">
+      <c r="AY96" t="inlineStr">
         <is>
           <t>O evento associado ao perfil @bugiocentro menciona que o 'Samba da Democracia' acontece no 'Largo da Antonieta', e a página do evento identifica o local como Bugio Centro, com endereço na Rua Victor Meirelles, 112, Centro, Florianópolis. Outra fonte também relaciona o Largo da Antonieta ao Bugio Centro na Rua Victor Meirelles.</t>
         </is>
@@ -18578,18 +18998,23 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU97" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV97" t="inlineStr">
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>https://scontent-mxp2-1.cdninstagram.com/v/t51.82787-15/798687167_18102299000620922_8305340148328867928_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4MDQ3MjAzMDE5NTIxNjY5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ivbKNXqk7NsQ7kNvwGcYxKy&amp;_nc_oc=AdrJXwXH7Gak6bZYVc9OS4rsQXbfmu_DjhrCMolN5_Swr5bzV-7s5tq_7wnyqHSh4Yc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mxp2-1.cdninstagram.com&amp;_nc_gid=6NVjIO6ILDyLaJrTDzsfyg&amp;_nc_ss=7a22e&amp;oh=00_AQJ9EXSZQqnVmcUUcEwWr9ueWmzxsE_i6sqx58dpzIQEPg&amp;oe=6AACECC3</t>
+        </is>
+      </c>
+      <c r="AV97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW97" t="inlineStr">
         <is>
           <t>https://www.baiacudealguem.com.br/pescadores-de-cultura/</t>
         </is>
       </c>
-      <c r="AW97" t="n">
+      <c r="AX97" t="n">
         <v>0.97</v>
       </c>
-      <c r="AX97" t="inlineStr">
+      <c r="AY97" t="inlineStr">
         <is>
           <t>A página oficial do Baiacu de Alguém informa explicitamente o espaço cultural e o endereço Rua Padre Lourenço R. de Andrade, 650 – Santo Antônio de Lisboa – Florianópolis (SC). Outra fonte de evento confirma o mesmo local e o bairro.</t>
         </is>
@@ -18784,18 +19209,23 @@
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
-      <c r="AU98" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV98" t="inlineStr">
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>https://scontent-mad2-1.cdninstagram.com/v/t51.82787-15/798537741_17953688934250034_8582485366033775767_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4MDQ3Mjk2OTU0MzAzMDg2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4XM8fQpcEYcQ7kNvwGU5mYL&amp;_nc_oc=AdrevwQpMUPsmUyRJBiGsbpmnzHY2hI9mpW3UubJlAwLNM9N3hvt2f0BRXYlkpx10mc&amp;_nc_ad=z-m&amp;_nc_cid=3033&amp;_nc_zt=23&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_gid=lMR0m9ZKH1fqxbUg3b3veg&amp;_nc_ss=7a22e&amp;oh=00_AQLnnRyO_LretNX2R_vWdThnuwAN_Nct9ITXC_6yBhJ74Q&amp;oe=6AAD1142</t>
+        </is>
+      </c>
+      <c r="AV98" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW98" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/servicos/comer-e-beber/bares-pubs-cerveja/bugio-centro</t>
         </is>
       </c>
-      <c r="AW98" t="n">
+      <c r="AX98" t="n">
         <v>0.95</v>
       </c>
-      <c r="AX98" t="inlineStr">
+      <c r="AY98" t="inlineStr">
         <is>
           <t xml:space="preserve">Há evidência consistente de que o espaço é o Bugio Centro, com endereço em R. Victor Meirelles, 112, no Centro de Florianópolis. A fonte consultada lista explicitamente o endereço e o bairro, compatíveis com o local informado e com referências adicionais encontradas em outras páginas. </t>
         </is>
@@ -18978,12 +19408,17 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV99" t="inlineStr"/>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>https://instagram.fsyd12-1.fna.fbcdn.net/v/t51.82787-15/798261819_18473646982115878_6092164994794218406_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3OTkyMDc4MTAxMDE3NzQxOTE4NDczNjQ2OTc5MTE1ODc4.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEyODQuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzIifQ%3D%3D&amp;_nc_ohc=Xj6zl-ZN2fIQ7kNvwEEcmjX&amp;_nc_oc=AdrfaCnJaoWeeLI7EA4WrDNa5XMK6dJcStLkGnc0VCx8c3Sq8Qqs78A84vfpopYe9Bc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fsyd12-1.fna&amp;_nc_gid=fvk8I0yxw7p0gR22FGBWpg&amp;_nc_ss=7a22e&amp;oh=00_AQK97CrmNog63AABx3aRujO_350ZZ52b1ceOSxIU6rs-xg&amp;oe=6AAD0979</t>
+        </is>
+      </c>
+      <c r="AV99" t="b">
+        <v>1</v>
+      </c>
       <c r="AW99" t="inlineStr"/>
-      <c r="AX99" t="inlineStr">
+      <c r="AX99" t="inlineStr"/>
+      <c r="AY99" t="inlineStr">
         <is>
           <t>Não encontrei evidência confiável o bastante para associar com segurança o perfil @bugiocentro a um estabelecimento/endereço específico em Florianópolis. Os resultados recuperados não confirmam o local informado nem trazem uma identificação direta do espaço. Para evitar inventar endereço, retornei null.</t>
         </is>
@@ -19148,18 +19583,23 @@
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
-      <c r="AU100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV100" t="inlineStr">
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>https://instagram.fadl7-2.fna.fbcdn.net/v/t51.82787-15/796582535_18102180575620922_7659603309728984920_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3OTg5MTI5MTU5NTA1NTMwOTE4MTAyMTgwNTcyNjIwOTIy.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjExNzAuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=isCoHkv3rEsQ7kNvwF86xM7&amp;_nc_oc=AdovJyAG0RBatquOgnfHezUtnH4OPPqVFPIu-VoHGJyPOkw04vNzjOUip02pYyqKNdU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl7-2.fna&amp;_nc_gid=BNgpocSDkC5yddBwDu-7vQ&amp;_nc_ss=7a22e&amp;oh=00_AQJVQ6iMJuYGllSR4XXurORPZ78DTF_fF4IDes4Xu7OvNg&amp;oe=6AACF0C9</t>
+        </is>
+      </c>
+      <c r="AV100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW100" t="inlineStr">
         <is>
           <t>https://devportal.pmf.sc.gov.br/entidades/cultura/index.php?noti=27706&amp;pagina=notpagina</t>
         </is>
       </c>
-      <c r="AW100" t="n">
+      <c r="AX100" t="n">
         <v>0.96</v>
       </c>
-      <c r="AX100" t="inlineStr">
+      <c r="AY100" t="inlineStr">
         <is>
           <t>A fonte da Prefeitura de Florianópolis informa explicitamente que o 1° Festival Literário e Cultural de Mulheres Escritoras ocorreu no Largo da Alfândega. Como o evento solicitado é um festival literário em Florianópolis e a evidência mais confiável encontrada aponta para esse local, o espaço provável é o Largo da Alfândega, no bairro Centro. Não encontrei evidência confiável adicional para outro endereço específico associado ao evento.</t>
         </is>
@@ -19338,12 +19778,17 @@
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
-      <c r="AU101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV101" t="inlineStr"/>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>https://instagram.fmid1-4.fna.fbcdn.net/v/t51.82787-15/797903916_18328065433277782_644530512022849116_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3OTY1MjU5OTczMjQ1NzAyMDE4MzI4MDY1NDMwMjc3Nzgy.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=t6b9tDCwz28Q7kNvwH8Pya4&amp;_nc_oc=AdphUZRIt6puhXkOE29O4laP6pEjAn2RnGkOXfCBcLOWYVQhm_rOLVyS-L1hG2GPwds&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmid1-4.fna&amp;_nc_gid=9xD8vo9fCN-RpDhiWcn1cA&amp;_nc_ss=7a22e&amp;oh=00_AQKVySxKMV3ft7L83Gj-6qzU82hJBsDC3hVaxnAoQbWikQ&amp;oe=6AAD142F</t>
+        </is>
+      </c>
+      <c r="AV101" t="b">
+        <v>1</v>
+      </c>
       <c r="AW101" t="inlineStr"/>
       <c r="AX101" t="inlineStr"/>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19522,12 +19967,17 @@
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
-      <c r="AU102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV102" t="inlineStr"/>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg4-2.cdninstagram.com/v/t51.82787-15/797471398_18018165959923638_2020689971933946965_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3OTU3MjUxMTk1ODk3MDU4NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7CrGYFAGMiYQ7kNvwFqj7G5&amp;_nc_oc=AdptoPDoq6iE7YpnEyCt_c5-GwbIapEp6JOsGzU9WWXle85gBnJStcR4Kg2cpdP3KGx4MzETnfnchz0EzqAlmzSa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_gid=W0ff41uguApcD0cXCL3Kog&amp;_nc_ss=7a22e&amp;oh=00_AQLW--4We-TijAguoatgUPdCOwZj2C6Be0o58ja25nbQpg&amp;oe=6AACE6E0</t>
+        </is>
+      </c>
+      <c r="AV102" t="b">
+        <v>1</v>
+      </c>
       <c r="AW102" t="inlineStr"/>
       <c r="AX102" t="inlineStr"/>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19714,12 +20164,17 @@
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
-      <c r="AU103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV103" t="inlineStr"/>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>https://instagram.fyzd1-2.fna.fbcdn.net/v/t51.82787-15/798455487_18473553052115878_6283757587276317198_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3OTUzOTAyMzYyMTEwNTk1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vfZcV5jFLQ0Q7kNvwEfS4lL&amp;_nc_oc=Adq028G9kIaPd8uinV2AL91FxkzMI6UVPw748pEgHnAzDVc_acYB8s1OmeEvFnnlitk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyzd1-2.fna&amp;_nc_gid=bTxJVS8hofXHeXhIamlBLQ&amp;_nc_ss=7a22e&amp;oh=00_AQLDpSab6-TWxNMg-Xhklp16sHfIU_zF9OqZ8h3UnwiW-w&amp;oe=6AAD0A56</t>
+        </is>
+      </c>
+      <c r="AV103" t="b">
+        <v>1</v>
+      </c>
       <c r="AW103" t="inlineStr"/>
       <c r="AX103" t="inlineStr"/>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19906,12 +20361,17 @@
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
-      <c r="AU104" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV104" t="inlineStr"/>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>https://instagram.fyzd1-2.fna.fbcdn.net/v/t51.82787-15/798455487_18473553052115878_6283757587276317198_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3OTUzOTAyMzYyMTEwNTk1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vfZcV5jFLQ0Q7kNvwEfS4lL&amp;_nc_oc=Adq028G9kIaPd8uinV2AL91FxkzMI6UVPw748pEgHnAzDVc_acYB8s1OmeEvFnnlitk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyzd1-2.fna&amp;_nc_gid=bTxJVS8hofXHeXhIamlBLQ&amp;_nc_ss=7a22e&amp;oh=00_AQLDpSab6-TWxNMg-Xhklp16sHfIU_zF9OqZ8h3UnwiW-w&amp;oe=6AAD0A56</t>
+        </is>
+      </c>
+      <c r="AV104" t="b">
+        <v>1</v>
+      </c>
       <c r="AW104" t="inlineStr"/>
       <c r="AX104" t="inlineStr"/>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -20098,12 +20558,17 @@
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
-      <c r="AU105" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV105" t="inlineStr"/>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>https://instagram.fyzd1-2.fna.fbcdn.net/v/t51.82787-15/798455487_18473553052115878_6283757587276317198_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3OTUzOTAyMzYyMTEwNTk1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vfZcV5jFLQ0Q7kNvwEfS4lL&amp;_nc_oc=Adq028G9kIaPd8uinV2AL91FxkzMI6UVPw748pEgHnAzDVc_acYB8s1OmeEvFnnlitk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyzd1-2.fna&amp;_nc_gid=bTxJVS8hofXHeXhIamlBLQ&amp;_nc_ss=7a22e&amp;oh=00_AQLDpSab6-TWxNMg-Xhklp16sHfIU_zF9OqZ8h3UnwiW-w&amp;oe=6AAD0A56</t>
+        </is>
+      </c>
+      <c r="AV105" t="b">
+        <v>1</v>
+      </c>
       <c r="AW105" t="inlineStr"/>
       <c r="AX105" t="inlineStr"/>
+      <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20290,12 +20755,17 @@
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
-      <c r="AU106" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV106" t="inlineStr"/>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>https://instagram.fyzd1-2.fna.fbcdn.net/v/t51.82787-15/798455487_18473553052115878_6283757587276317198_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3OTUzOTAyMzYyMTEwNTk1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vfZcV5jFLQ0Q7kNvwEfS4lL&amp;_nc_oc=Adq028G9kIaPd8uinV2AL91FxkzMI6UVPw748pEgHnAzDVc_acYB8s1OmeEvFnnlitk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyzd1-2.fna&amp;_nc_gid=bTxJVS8hofXHeXhIamlBLQ&amp;_nc_ss=7a22e&amp;oh=00_AQLDpSab6-TWxNMg-Xhklp16sHfIU_zF9OqZ8h3UnwiW-w&amp;oe=6AAD0A56</t>
+        </is>
+      </c>
+      <c r="AV106" t="b">
+        <v>1</v>
+      </c>
       <c r="AW106" t="inlineStr"/>
       <c r="AX106" t="inlineStr"/>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20482,12 +20952,17 @@
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
-      <c r="AU107" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV107" t="inlineStr"/>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>https://instagram.fyzd1-2.fna.fbcdn.net/v/t51.82787-15/798455487_18473553052115878_6283757587276317198_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3OTUzOTAyMzYyMTEwNTk1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vfZcV5jFLQ0Q7kNvwEfS4lL&amp;_nc_oc=Adq028G9kIaPd8uinV2AL91FxkzMI6UVPw748pEgHnAzDVc_acYB8s1OmeEvFnnlitk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyzd1-2.fna&amp;_nc_gid=bTxJVS8hofXHeXhIamlBLQ&amp;_nc_ss=7a22e&amp;oh=00_AQLDpSab6-TWxNMg-Xhklp16sHfIU_zF9OqZ8h3UnwiW-w&amp;oe=6AAD0A56</t>
+        </is>
+      </c>
+      <c r="AV107" t="b">
+        <v>1</v>
+      </c>
       <c r="AW107" t="inlineStr"/>
       <c r="AX107" t="inlineStr"/>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20674,12 +21149,17 @@
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
-      <c r="AU108" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV108" t="inlineStr"/>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>https://instagram.fyzd1-2.fna.fbcdn.net/v/t51.82787-15/798455487_18473553052115878_6283757587276317198_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3OTUzOTAyMzYyMTEwNTk1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vfZcV5jFLQ0Q7kNvwEfS4lL&amp;_nc_oc=Adq028G9kIaPd8uinV2AL91FxkzMI6UVPw748pEgHnAzDVc_acYB8s1OmeEvFnnlitk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyzd1-2.fna&amp;_nc_gid=bTxJVS8hofXHeXhIamlBLQ&amp;_nc_ss=7a22e&amp;oh=00_AQLDpSab6-TWxNMg-Xhklp16sHfIU_zF9OqZ8h3UnwiW-w&amp;oe=6AAD0A56</t>
+        </is>
+      </c>
+      <c r="AV108" t="b">
+        <v>1</v>
+      </c>
       <c r="AW108" t="inlineStr"/>
       <c r="AX108" t="inlineStr"/>
+      <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20870,12 +21350,17 @@
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
-      <c r="AU109" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV109" t="inlineStr"/>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>https://instagram.fyzd1-2.fna.fbcdn.net/v/t51.82787-15/798455487_18473553052115878_6283757587276317198_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3OTUzOTAyMzYyMTEwNTk1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=vfZcV5jFLQ0Q7kNvwEfS4lL&amp;_nc_oc=Adq028G9kIaPd8uinV2AL91FxkzMI6UVPw748pEgHnAzDVc_acYB8s1OmeEvFnnlitk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyzd1-2.fna&amp;_nc_gid=bTxJVS8hofXHeXhIamlBLQ&amp;_nc_ss=7a22e&amp;oh=00_AQLDpSab6-TWxNMg-Xhklp16sHfIU_zF9OqZ8h3UnwiW-w&amp;oe=6AAD0A56</t>
+        </is>
+      </c>
+      <c r="AV109" t="b">
+        <v>1</v>
+      </c>
       <c r="AW109" t="inlineStr"/>
       <c r="AX109" t="inlineStr"/>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -21038,18 +21523,23 @@
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
-      <c r="AU110" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV110" t="inlineStr">
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>https://instagram.fyvr3-1.fna.fbcdn.net/v/t51.82787-15/795462847_18102032630620922_112374683117963251_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3OTEyMDgwODYzNzQzOTMxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=2ZxWaDaUKz4Q7kNvwECg6xQ&amp;_nc_oc=AdqrwJSo4j1kb8XARNI8RNFerONoZhFoNCnnktETpW4Cq-4hDbN0foEHnOBtBtwrh3F7k8bYx7qYIir8JCxjNKmB&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyvr3-1.fna&amp;_nc_gid=TPlLuTG8NrmLuP8DJd4MrA&amp;_nc_ss=7a22e&amp;oh=00_AQK-BFODBG8dBTg0pnhaNijZ1mJzmHW5Kwn6S3LxO0aDSQ&amp;oe=6AACF6A3</t>
+        </is>
+      </c>
+      <c r="AV110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW110" t="inlineStr">
         <is>
           <t>https://www.somosaldeia.com.br/eventos/fl-1o-festival-literario-e-cultural-de-mulheres-escritoras-um-tributo-a-antonieta-de-barros</t>
         </is>
       </c>
-      <c r="AW110" t="n">
+      <c r="AX110" t="n">
         <v>0.88</v>
       </c>
-      <c r="AX110" t="inlineStr">
+      <c r="AY110" t="inlineStr">
         <is>
           <t>Encontrei evidência confiável de um festival literário em Florianópolis no Largo da Alfândega, com bairro Centro, na página do evento da Aldeia. Porém, não localizei endereço completo consistente na fonte consultada; por isso, retorno apenas o local provável e o bairro, sem inventar o endereço.</t>
         </is>
@@ -21236,18 +21726,23 @@
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
-      <c r="AU111" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV111" t="inlineStr">
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>https://scontent-nrt6-1.cdninstagram.com/v/t51.82787-15/792133784_18280140874290806_6118934494751441508_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3OTAzNzMyNzQxNzY1NTA5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BgylD8RmLAIQ7kNvwFko91o&amp;_nc_oc=Adpq87XktrNOklWE1VkfrK-w1LlTLoL7EjH_IEFl1iO8Nsc-KAalO50rpsPq6uWINDo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=gT3E2kmNiZbGliITdogo7A&amp;_nc_ss=7a22e&amp;oh=00_AQJVHWFq9ydh9idJJXAFd9M-d8B7rBAHhxAQyp3ULvyoIQ&amp;oe=6AAD06E9</t>
+        </is>
+      </c>
+      <c r="AV111" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW111" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/servicos/comer-e-beber/o-araca-botequim.php</t>
         </is>
       </c>
-      <c r="AW111" t="n">
+      <c r="AX111" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX111" t="inlineStr">
+      <c r="AY111" t="inlineStr">
         <is>
           <t>A busca por "Samba do Araçá" em Florianópolis aponta para o perfil @oaracabotequim e para páginas que identificam o espaço como O Araçá Botequim na Lagoa da Conceição, com endereço em R. Manoel Severino de Oliveira, 19. Como há correspondência direta entre o nome do evento e o nome do estabelecimento, esta é a identificação mais provável.</t>
         </is>
@@ -21430,12 +21925,17 @@
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
-      <c r="AU112" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV112" t="inlineStr"/>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t51.82787-15/792053730_18327924421277782_263825038579235380_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3ODk0NDkyMTQzNjMxOTU4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjczMC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=gKr8SGjQRbIQ7kNvwG4gtO5&amp;_nc_oc=AdpHGvL1j1C-Pr0qy-B5OpVNqV46ZZ2dPFbjrLjI21hZAFvhd0B0BE_CnTBuJU6nWes&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=78vYCelg_JSaIOeRJryN4A&amp;_nc_ss=7a22e&amp;oh=00_AQLI177UnUPteL6BZoVBbM6oGCqWuOt4OGUpsRGhUfdV6A&amp;oe=6AAD0B15</t>
+        </is>
+      </c>
+      <c r="AV112" t="b">
+        <v>1</v>
+      </c>
       <c r="AW112" t="inlineStr"/>
       <c r="AX112" t="inlineStr"/>
+      <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -21610,18 +22110,23 @@
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
-      <c r="AU113" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV113" t="inlineStr">
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>https://instagram.fbcn4-1.fna.fbcdn.net/v/t51.82787-15/795913058_18132789367730262_5836977966635991083_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3ODk5MDkzODQwNzc0NzI5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuNzIyLnNkci5yZWd1bGFyX3Bob3RvLkMzIn0%3D&amp;_nc_ohc=JWUNAEnFy_oQ7kNvwFB1-7d&amp;_nc_oc=AdrWPVF5Gnjw2JbPr0qltFuBW7yCPbLzSO_WmsXKlEmbL73Sd8A-8Ppf1JmtVuLjB_4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbcn4-1.fna&amp;_nc_gid=SN_mmy9ePy5bPd2ERdqdeg&amp;_nc_ss=7a22e&amp;oh=00_AQLVS-NXyN-T6RPqCJ8a0HwMwetaG0yNpT5aoR8NZ4pYzA&amp;oe=6AACEEFA</t>
+        </is>
+      </c>
+      <c r="AV113" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW113" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com.br/Restaurant_Review-g303576-d33047585-Reviews-Bugio_Centro-Florianopolis_State_of_Santa_Catarina.html</t>
         </is>
       </c>
-      <c r="AW113" t="n">
+      <c r="AX113" t="n">
         <v>0.86</v>
       </c>
-      <c r="AX113" t="inlineStr">
+      <c r="AY113" t="inlineStr">
         <is>
           <t>Há evidência confiável de que o local informado 'Bugio' corresponde ao Bugio Centro em Florianópolis, com endereço consistente em múltiplas fontes consultadas. Não encontrei evidência confiável indicando outro espaço mais provável para o evento da Kumba Groove.</t>
         </is>
@@ -21796,18 +22301,23 @@
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
-      <c r="AU114" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV114" t="inlineStr">
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW114" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/servicos/comer-e-beber/bares-pubs-cerveja/bugio-centro</t>
         </is>
       </c>
-      <c r="AW114" t="n">
+      <c r="AX114" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX114" t="inlineStr">
+      <c r="AY114" t="inlineStr">
         <is>
           <t>Há evidência confiável de que o “salão da Bugio” se refere ao Bugio Centro, em Florianópolis, com endereço na Rua Victor Meirelles, 112, no Centro. A fonte consultada também descreve o espaço como localizado no Centro de Florianópolis e bate com a referência ao perfil @bugiolab e ao uso de “salão” em eventos do local.</t>
         </is>
@@ -21984,18 +22494,23 @@
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
-      <c r="AU115" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV115" t="inlineStr">
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV115" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW115" t="inlineStr">
         <is>
           <t>https://troop.is/events/naddr1qvzqqqrukvpzp08t5xjg49jvqg77q54d5smmjastaq8d85zzuwtzdzr0m6fd0z0xqqsxxcecxgun2dp5vscnsvejxqerzwfhxvekydpsv5ursvtyxe3kvcggq9v23</t>
         </is>
       </c>
-      <c r="AW115" t="n">
+      <c r="AX115" t="n">
         <v>0.89</v>
       </c>
-      <c r="AX115" t="inlineStr">
+      <c r="AY115" t="inlineStr">
         <is>
           <t>O evento associado à mesma programação de setembro menciona 'Encontro Coletiva Linha dos Desterro — Gratuito na rua' e aponta o local como Bugic/Bugio Lab em Florianópolis. Outra fonte confirma o endereço 'R. Victor Meirelles, 112, segundo piso da Bugio Centro', e uma publicação adicional identifica 'Bugio Bar – Centro Histórico de Florianópolis (Rua Victor Meirelles, 112 – Centro – Florianópolis – SC)'. Como a referência indica que o encontro é 'na rua', o espaço provável é o entorno da Bugio Centro/Bugio Lab, no Centro.</t>
         </is>
@@ -22186,18 +22701,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU116" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV116" t="inlineStr">
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW116" t="inlineStr">
         <is>
           <t>https://www.querole.net/events/1-Florian%C3%B3polis/2026-08-15</t>
         </is>
       </c>
-      <c r="AW116" t="n">
+      <c r="AX116" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX116" t="inlineStr">
+      <c r="AY116" t="inlineStr">
         <is>
           <t>Encontrei menções consistentes ao espaço como 'Bugio Lab' e também como 'Bugio Centro / Bugio Bar', todas associadas ao endereço 'R. Victor Meirelles, 112' em Florianópolis, com indicação explícita de 'segundo piso' em uma das fontes. O bairro aparece como Centro em fontes que vinculam esse endereço ao espaço. A evidência é convergente, embora o nome do estabelecimento varie entre Bugio Lab e Bugio Centro/Bugio Bar.</t>
         </is>
@@ -22384,18 +22904,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU117" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV117" t="inlineStr">
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV117" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW117" t="inlineStr">
         <is>
           <t>https://guiafloripa.com.br/servicos/comer-e-beber/bares-pubs-cerveja/bugio-centro</t>
         </is>
       </c>
-      <c r="AW117" t="n">
+      <c r="AX117" t="n">
         <v>0.68</v>
       </c>
-      <c r="AX117" t="inlineStr">
+      <c r="AY117" t="inlineStr">
         <is>
           <t>Encontrei evidência confiável para o espaço Bugio no Centro de Florianópolis e para o endereço na Rua Victor Meirelles, 112. A fonte local consultada aponta o Bugio Centro em Florianópolis, e outras referências indicam o número 112 na Rua Victor Meirelles no Centro. Não achei confirmação forte e direta do nome exato 'Bugio Lab' na mesma URL, então tratei como provável correspondência do espaço e mantive o bairro como Centro.</t>
         </is>
@@ -22582,18 +23107,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU118" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV118" t="inlineStr">
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV118" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW118" t="inlineStr">
         <is>
           <t>https://cervejariabugio.com.br/en</t>
         </is>
       </c>
-      <c r="AW118" t="n">
+      <c r="AX118" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AX118" t="inlineStr">
+      <c r="AY118" t="inlineStr">
         <is>
           <t>O site oficial informa que o espaço fica em Florianópolis, na Rua Victor Meirelles, 112, e identifica o local como Centro Histórico. Outras fontes de apoio também associam o endereço ao bairro Centro.</t>
         </is>
@@ -22784,18 +23314,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU119" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV119" t="inlineStr">
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV119" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW119" t="inlineStr">
         <is>
           <t>https://secarte.ufsc.br/agenda-cultural/action~agenda/time_limit~549774000/cat_ids~58708%2C243834%2C47/request_format~html/</t>
         </is>
       </c>
-      <c r="AW119" t="n">
+      <c r="AX119" t="n">
         <v>0.89</v>
       </c>
-      <c r="AX119" t="inlineStr">
+      <c r="AY119" t="inlineStr">
         <is>
           <t>Encontrei menções consistentes ao espaço como Bugio Lab/Bugio Centro na Rua Victor Meirelles, nº 112, em Florianópolis, com indicação de Centro como bairro. A fonte consultada e outros resultados convergem para esse endereço, mas não há confirmação direta do '2º andar' na fonte principal, então mantive apenas o endereço e bairro com base no que foi evidenciado.</t>
         </is>
@@ -22974,18 +23509,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU120" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV120" t="inlineStr">
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV120" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW120" t="inlineStr">
         <is>
           <t>https://tocaonde.com.br/events/78237-forro-de-base-delas-bugio-centro-florianopolis</t>
         </is>
       </c>
-      <c r="AW120" t="n">
+      <c r="AX120" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX120" t="inlineStr">
+      <c r="AY120" t="inlineStr">
         <is>
           <t>Há evidência consistente de que eventos de forró associados ao ecossistema Bugio em Florianópolis ocorrem no Bugio Centro/Bugio Lab. A fonte consultada informa o endereço Rua Victor Meirelles, 112 - Centro, Florianópolis - SC, e outras páginas de eventos recentes confirmam 'Bugio Lab' em Florianópolis para atividades semelhantes.</t>
         </is>
@@ -23170,18 +23710,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU121" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV121" t="inlineStr">
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV121" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW121" t="inlineStr">
         <is>
           <t>https://secarte.ufsc.br/agenda-cultural/action~agenda/time_limit~1718938800/cat_ids~32941%2C68191%2C58708%2C1682850%2C47/request_format~html/</t>
         </is>
       </c>
-      <c r="AW121" t="n">
+      <c r="AX121" t="n">
         <v>0.86</v>
       </c>
-      <c r="AX121" t="inlineStr">
+      <c r="AY121" t="inlineStr">
         <is>
           <t>Encontrei referência direta a 'Bugio Bar – Centro | Rua Victor Meirelles, nº112' em fonte institucional da UFSC/SeCArtE, e outra fonte menciona explicitamente 'Bugio Lab: R. Victor Meirelles, 112, segundo piso da Bugio Centro'. Isso sustenta o endereço informado e indica o bairro Centro. Não encontrei evidência confiável para um endereço diferente.</t>
         </is>
@@ -23366,18 +23911,23 @@
           <t>Existem candidatos concorrentes com pontuações semelhantes</t>
         </is>
       </c>
-      <c r="AU122" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV122" t="inlineStr">
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV122" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW122" t="inlineStr">
         <is>
           <t>https://cervejariabugio.com.br/en</t>
         </is>
       </c>
-      <c r="AW122" t="n">
+      <c r="AX122" t="n">
         <v>0.92</v>
       </c>
-      <c r="AX122" t="inlineStr">
+      <c r="AY122" t="inlineStr">
         <is>
           <t>Encontrei evidência consistente de que o espaço fica na Rua Victor Meirelles, 112, no Centro Histórico de Florianópolis. A página oficial da Bugio informa o endereço; outra fonte de evento cita “Bugio Lab: R. Victor Meirelles, 112, segundo piso da Bugio Centro”. O bairro identificado nas fontes é Centro. Não inventei endereço além do que foi encontrado.</t>
         </is>
@@ -23560,18 +24110,23 @@
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
-      <c r="AU123" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV123" t="inlineStr">
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.82787-15/796941348_17953371897250034_3781261788593233695_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3ODk1NzEwNzAxNzI0MjE1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=1jCjvdT4XxgQ7kNvwHGL8MJ&amp;_nc_oc=Adqd7xs_xeOEMfGgKA--V7HTLng1Al0nMCQd__E1P8FVu0uO1p0D84co75AQv-gZNlI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=1VybPjbobaf5j0deIO7cIQ&amp;_nc_ss=7a22e&amp;oh=00_AQKz5o3H1K0r65v04xnL96HjDQfUS7I83Do5ICcwwqALwA&amp;oe=6AAD0893</t>
+        </is>
+      </c>
+      <c r="AV123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW123" t="inlineStr">
         <is>
           <t>https://cervejariabugio.com.br/en</t>
         </is>
       </c>
-      <c r="AW123" t="n">
+      <c r="AX123" t="n">
         <v>0.91</v>
       </c>
-      <c r="AX123" t="inlineStr">
+      <c r="AY123" t="inlineStr">
         <is>
           <t>Encontrei fonte oficial da própria Bugio informando que o espaço 'Centro Bugio' fica na Rua Victor Meirelles, 112, Centro Histórico. Outras fontes de apoio também associam a Rua Victor Meirelles, 112 ao bairro Centro em Florianópolis. O perfil informado @bugiolab e o nome do evento apontam para esse mesmo local.</t>
         </is>
@@ -23754,12 +24309,17 @@
           <t>Baixa compatibilidade entre o evento e o local encontrado</t>
         </is>
       </c>
-      <c r="AU124" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV124" t="inlineStr"/>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/794225821_18018011108923638_5268044950156665892_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3ODgzMjc0MjIwMzMwNDg4OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DmmcGHgv1LMQ7kNvwFh3Op-&amp;_nc_oc=AdrNDFo-rSvA2MRaRXyJcJDHPaYbm5YpcP62V_8fgfX5JaTvVf-rzQD67yn-RBRtiv_WlyL1bbtsKv4VA-YwiPLU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=rjngGqk4NmdP_O-lDgpKNQ&amp;_nc_ss=7a22e&amp;oh=00_AQL43A-E8LKiPV2V1iV4axjEOyYEieuYZ9V7YmPfekFcLA&amp;oe=6AAD055D</t>
+        </is>
+      </c>
+      <c r="AV124" t="b">
+        <v>1</v>
+      </c>
       <c r="AW124" t="inlineStr"/>
-      <c r="AX124" t="inlineStr">
+      <c r="AX124" t="inlineStr"/>
+      <c r="AY124" t="inlineStr">
         <is>
           <t>Não encontrei evidência confiável e específica que conecte o perfil @bugiotrindade ao local do evento “Forró da Xepa” nem um endereço verificável do estabelecimento/espaço. As buscas retornaram resultados irrelevantes ou genéricos, sem confirmação do local informado. Portanto, por cautela, retorno null.</t>
         </is>
